--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="N13" s="17" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>原則①：原因を追える</t>
+          <t>原則①：原因を追える（変更ソース）</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>変更の経路が記録される</t>
+          <t>変更の経路（変更ソース）が履歴に記録され、絞り込めること</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>4種すべてが記録・絞り込み可能</t>
+          <t>【T-H02の②】手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)の4種すべてが記録され、絞り込みできる</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>予約行で 変更反映日時 ≠ 編集日時</t>
+          <t>【T-H02の①】予約した行で 変更反映日時 ≠ 編集日時 になる（例：反映8/1・編集6/25）</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -1577,67 +1577,67 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>M1 過去が動かない構造ができる</t>
+          <t>M2 金額が算式どおりに出る</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>設定が適用日付つきで保存され、履歴が積まれる。同じ従業員コードが二重に登録されない</t>
+          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>原則①：どの入口でも履歴が残る</t>
+          <t>原則③：人件費は働いた店舗に付ける</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>AC-49</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>L1 MVP必須</t>
+          <t>AC-11</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>L0 リリース不可</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>どの入口から設定を編集しても、適用日付と設定変更履歴が同じように記録されること</t>
+          <t>店舗別の合計が全社の実績給与と一致する</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される</t>
+          <t>店舗5店の合計 − 全社 = 0円（1,461,312円）</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>不可（片方だけ履歴が残らないと変更を追えない期間ができ、AC-07・AC-03に連鎖）</t>
+          <t>★中止（店舗別PLが使えない）</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>設定更新の処理を1箇所に集約し、両方の画面から同じ処理を呼ぶ。画面ごとに別の更新処理を持たない</t>
+          <t>ヘルプ人件費を「実績給与×ヘルプ時間÷総労働時間」で按分し、端数を所属店舗に寄せる（判断9）。加算のみの実装は不可</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（設定編集モーダル）／従業員詳細</t>
+          <t>人件費実績（月別・実績）</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>T-A09 R-06</t>
+          <t>S-02 C-005 R-04</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
+          <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
         </is>
       </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>S-02.png</t>
         </is>
       </c>
       <c r="N21" s="17" t="inlineStr"/>
@@ -1658,57 +1658,57 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>原則③：人件費は働いた店舗に付ける</t>
+          <t>原則①：予約が自動で効く</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>L0 リリース不可</t>
+          <t>AC-05</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社の実績給与と一致する</t>
+          <t>適用日を迎えたら自動で切り替わる</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>店舗5店の合計 − 全社 = 0円（1,461,312円）</t>
+          <t>適用日00:00以降に新値・ステータスが「適用中」</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>★中止（店舗別PLが使えない）</t>
+          <t>不可（毎日手作業になる）</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>ヘルプ人件費を「実績給与×ヘルプ時間÷総労働時間」で按分し、端数を所属店舗に寄せる（判断9）。加算のみの実装は不可</t>
+          <t>日次バッチまたは参照時解決のいずれかで、適用日到来を人手なしに反映する</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（月別・実績）</t>
+          <t>従業員一覧／設定履歴</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>S-02 C-005 R-04</t>
+          <t>T-D05</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
+          <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>S-02.png</t>
+          <t>T-D05.png</t>
         </is>
       </c>
       <c r="N22" s="17" t="inlineStr"/>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>原則①：予約が自動で効く</t>
+          <t>計算：算式どおりの金額</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>AC-05</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
@@ -1744,42 +1744,42 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>適用日を迎えたら自動で切り替わる</t>
+          <t>実績給与が算式の計算値と一致する</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>適用日00:00以降に新値・ステータスが「適用中」</t>
+          <t>全行で差分=0円（EMP-001=338,000／EMP-002=285,250／EMP-003=144,000／EMP-005=382,812／EMP-007=311,250）</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>不可（毎日手作業になる）</t>
+          <t>不可（数字の根拠が説明できない）</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>日次バッチまたは参照時解決のいずれかで、適用日到来を人手なしに反映する</t>
+          <t>実績給与＝概算給与＋深夜残業代＋みなし超過残業代。交通費は含めない</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>従業員一覧／設定履歴</t>
+          <t>人件費実績（月別・実績）</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>T-D05</t>
+          <t>S-02 S-03 T-A02 T-A05 C-001 C-003 C-013</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
+          <t>§第5部 11-A 確定した算式</t>
         </is>
       </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
-          <t>T-D05.png</t>
+          <t>S-02.png</t>
         </is>
       </c>
       <c r="N23" s="17" t="inlineStr"/>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額</t>
+          <t>計算：月中改定の日割り</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-12</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
@@ -1815,32 +1815,32 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>実績給与が算式の計算値と一致する</t>
+          <t>所定労働日割で按分される</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>全行で差分=0円（EMP-001=338,000／EMP-002=285,250／EMP-003=144,000／EMP-005=382,812／EMP-007=311,250）</t>
+          <t>332,727円（320,000×8/22＋340,000×14/22）</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>不可（数字の根拠が説明できない）</t>
+          <t>不可（予約機能が実用にならない）</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>実績給与＝概算給与＋深夜残業代＋みなし超過残業代。交通費は含めない</t>
+          <t>判断1＝所定労働日割。分母は当月の所定労働日数。暦日割の実装は不可</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（月別・実績）</t>
+          <t>人件費実績（月別・概算）</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>S-02 S-03 T-A02 T-A05 C-001 C-003 C-013</t>
+          <t>S-02 C-006</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>計算：月中改定の日割り</t>
+          <t>計算：時給者</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>AC-12</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>所定労働日割で按分される</t>
+          <t>単価×所定労働時間になる</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>332,727円（320,000×8/22＋340,000×14/22）</t>
+          <t>144,000円（差分0）</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>不可（予約機能が実用にならない）</t>
+          <t>不可（概算が使えない）</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>判断1＝所定労働日割。分母は当月の所定労働日数。暦日割の実装は不可</t>
+          <t>時給者は日割り按分ではなく、各勤務日の有効単価で積む</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>S-02 C-006</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
-          <t>S-02.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="N25" s="17" t="inlineStr"/>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>計算：時給者</t>
+          <t>原則③：ヘルプ人件費</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-14</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -1957,42 +1957,42 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>単価×所定労働時間になる</t>
+          <t>働いた店舗・その日の有効単価で計算される</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>144,000円（差分0）</t>
+          <t>按分額が実績給与×ヘルプ時間÷総労働時間と一致</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>不可（概算が使えない）</t>
+          <t>不可（店舗別PLが実態とずれる）</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>時給者は日割り按分ではなく、各勤務日の有効単価で積む</t>
+          <t>日別の勤務店舗を保持し、店舗別集計時に振り替える</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（月別・概算）</t>
+          <t>人件費実績（日別）／月別</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-003 C-013</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>§第5部 11-A 確定した算式</t>
+          <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="N26" s="17" t="inlineStr"/>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>原則③：ヘルプ人件費</t>
+          <t>原則③：交通費の帰属</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>AC-14</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -2028,32 +2028,32 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>働いた店舗・その日の有効単価で計算される</t>
+          <t>交通費が独立費目として一意に計上される</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>按分額が実績給与×ヘルプ時間÷総労働時間と一致</t>
+          <t>実績給与に交通費を含まない／通勤は所属店舗・ヘルプ先は応援先に計上（店舗別合計100,000円）</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>不可（店舗別PLが実態とずれる）</t>
+          <t>不可（人件費の総額がずれる）</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>日別の勤務店舗を保持し、店舗別集計時に振り替える</t>
+          <t>判断6＝独立列。給与とは別カラムで持ち、総支給額＝給与＋交通費で表示</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（日別）／月別</t>
+          <t>人件費実績（月別・日別）</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>C-003 C-013</t>
+          <t>S-02 T-R04 C-017</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="M27" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>S-02.png</t>
         </is>
       </c>
       <c r="N27" s="17" t="inlineStr"/>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>原則③：交通費の帰属</t>
+          <t>入出力：勤怠実績を取り込める</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
@@ -2099,42 +2099,42 @@
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>交通費が独立費目として一意に計上される</t>
+          <t>「実績データ取込」で勤怠実績が取り込まれ、人件費実績に反映されること</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>実績給与に交通費を含まない／通勤は所属店舗・ヘルプ先は応援先に計上（店舗別合計100,000円）</t>
+          <t>取込後に実績モードの金額が表示される（未反映=0件）。取込中は画面を操作できない</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>不可（人件費の総額がずれる）</t>
+          <t>不可（実績の数字が出ず、締めも意味を持たない）</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>判断6＝独立列。給与とは別カラムで持ち、総支給額＝給与＋交通費で表示</t>
+          <t>取込処理を非同期で実行し、進捗を返す。処理中は締めなど後続の操作を受け付けない</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（月別・日別）</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>S-02 T-R04 C-017</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
+          <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>S-02.png</t>
+          <t>T-A08.png</t>
         </is>
       </c>
       <c r="N28" s="17" t="inlineStr"/>
@@ -2145,67 +2145,67 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>M2 金額が算式どおりに出る</t>
+          <t>M3 月次を確定して外部へ渡せる</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
+          <t>締めた月は動かず、解除すれば再計算される。締めは会社スコープのみ</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>入出力：勤怠実績を取り込める</t>
+          <t>原則②：締めたら動かない</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>AC-48</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>L1 MVP必須</t>
+          <t>AC-16</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>L0 リリース不可</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>「実績データ取込」で勤怠実績が取り込まれ、人件費実績に反映されること</t>
+          <t>締め済みの月の数字が動かない</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>取込後に実績モードの金額が表示される（未反映=0件）。取込中は画面を操作できない</t>
+          <t>当月の実績給与・総労働時間の差分=0円</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>不可（実績の数字が出ず、締めも意味を持たない）</t>
+          <t>★中止（締めの意味が消える）</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>取込処理を非同期で実行し、進捗を返す。処理中は締めなど後続の操作を受け付けない</t>
+          <t>締めフラグを持ち、締め済み期間は再計算をスキップする（設定変更・勤怠取込の両方）。スナップショットで固定</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>人件費実績（月別）</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>T-A08</t>
+          <t>T-S03 T-S04 C-008 R-02</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>§第2部 フロー1・8・9・10</t>
+          <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>T-A08.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="N29" s="17" t="inlineStr"/>
@@ -2226,37 +2226,37 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない</t>
+          <t>原則②：解除で再計算</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>AC-16</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>L0 リリース不可</t>
+          <t>AC-17</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>締め済みの月の数字が動かない</t>
+          <t>保留されていた変更が反映されて再計算される</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>当月の実績給与・総労働時間の差分=0円</t>
+          <t>解除後の実績給与＝改定を反映した計算値（差分0円）</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>★中止（締めの意味が消える）</t>
+          <t>不可（誤りを修正できない）</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>締めフラグを持ち、締め済み期間は再計算をスキップする（設定変更・勤怠取込の両方）。スナップショットで固定</t>
+          <t>解除で締めフラグを落とし、再計算をキューに入れる</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>T-S03 T-S04 C-008 R-02</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-S05.png</t>
         </is>
       </c>
       <c r="N30" s="17" t="inlineStr"/>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>原則②：解除で再計算</t>
+          <t>原則②：締めの単位は月</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>AC-17</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr">
@@ -2312,32 +2312,32 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>保留されていた変更が反映されて再計算される</t>
+          <t>締めは月別タブにのみ表示される</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>解除後の実績給与＝改定を反映した計算値（差分0円）</t>
+          <t>日別タブでの表示=0</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>不可（誤りを修正できない）</t>
+          <t>条件付きGo可（誤解を招くが実害は小さい）</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>解除で締めフラグを落とし、再計算をキューに入れる</t>
+          <t>日別タブに締めUIを置かない</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>T-S01.png</t>
         </is>
       </c>
       <c r="N31" s="17" t="inlineStr"/>
@@ -2368,12 +2368,12 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>原則②：締めの単位は月</t>
+          <t>原則②：確定操作は確認を経る</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
@@ -2383,32 +2383,32 @@
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>締めは月別タブにのみ表示される</t>
+          <t>実行前に確認が入る</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>日別タブでの表示=0</t>
+          <t>確認モーダル=各1回</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（誤解を招くが実害は小さい）</t>
+          <t>条件付きGo可（誤操作リスクは残る）</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>日別タブに締めUIを置かない</t>
+          <t>締め・解除ともに確認を挟む</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>人件費実績（月別）</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-S03 T-S05</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>T-S01.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="N32" s="17" t="inlineStr"/>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>原則②：確定操作は確認を経る</t>
+          <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>AC-19</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
@@ -2454,32 +2454,32 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>実行前に確認が入る</t>
+          <t>警告が出て、黙って無視されない</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>確認モーダル=各1回</t>
+          <t>警告なしの保存=0件</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（誤操作リスクは残る）</t>
+          <t>不可（支払額と乖離する）</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>締め・解除ともに確認を挟む</t>
+          <t>締め済み期間への適用を検出して警告。既定は将来適用へ寄せる</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>従業員詳細</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>T-S03 T-S05</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-D07.png</t>
         </is>
       </c>
       <c r="N33" s="17" t="inlineStr"/>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>原則②：遡及は黙って捨てない</t>
+          <t>原則②：締めは会社スコープのみ</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
@@ -2525,32 +2525,32 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>警告が出て、黙って無視されない</t>
+          <t>店長は締めを実行できない</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>警告なしの保存=0件</t>
+          <t>店長での締め実行=0件（ボタン非表示または拒否）</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>不可（支払額と乖離する）</t>
+          <t>不可（月次が店舗ごとに分断される）</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>締め済み期間への適用を検出して警告。既定は将来適用へ寄せる</t>
+          <t>締めAPIを会社スコープ権限で制限。画面側だけで隠さない</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>人件費実績（月別）</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S07 R-02</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>T-D07.png</t>
+          <t>T-S07.png</t>
         </is>
       </c>
       <c r="N34" s="17" t="inlineStr"/>
@@ -2571,22 +2571,22 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>M3 月次を確定して外部へ渡せる</t>
+          <t>M4 顧客とCSが自分で運用できる</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>締めた月は動かず、解除すれば再計算される。締めは会社スコープのみ</t>
+          <t>CSVで取り込め、必要な項目だけ出力でき、原因を追える</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>原則②：締めは会社スコープのみ</t>
+          <t>入出力：導入を止めない</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
@@ -2596,42 +2596,42 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>店長は締めを実行できない</t>
+          <t>KOT形式のCSVが全行取り込める</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>店長での締め実行=0件（ボタン非表示または拒否）</t>
+          <t>取込成功=3行</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>不可（月次が店舗ごとに分断される）</t>
+          <t>不可（導入時に手入力になる）</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>締めAPIを会社スコープ権限で制限。画面側だけで隠さない</t>
+          <t>ヘッダー名で列を解決。テンプレートDLの列と一致させる</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>T-S07 R-02</t>
+          <t>T-I02 T-I03</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
+          <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>T-S07.png</t>
+          <t>T-I02.png</t>
         </is>
       </c>
       <c r="N35" s="17" t="inlineStr"/>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない</t>
+          <t>入出力：表記ゆれを吸収</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>KOT形式のCSVが全行取り込める</t>
+          <t>表記ゆれのヘッダーでも取り込める</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>不可（導入時に手入力になる）</t>
+          <t>不可（ジョブカン顧客の導入が止まる）</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>ヘッダー名で列を解決。テンプレートDLの列と一致させる</t>
+          <t>列マッピングで吸収する（コードに列名を埋め込まない）</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>T-I02 T-I03</t>
+          <t>T-I04 R-05</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>T-I02.png</t>
+          <t>T-I04.png</t>
         </is>
       </c>
       <c r="N36" s="17" t="inlineStr"/>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収</t>
+          <t>データ保全：不正値を入れない</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -2738,22 +2738,22 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>表記ゆれのヘッダーでも取り込める</t>
+          <t>異常が検出され、不正な値が登録されない</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>取込成功=3行</t>
+          <t>4行すべて検出（見逃し=0）</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>不可（ジョブカン顧客の導入が止まる）</t>
+          <t>不可（マスタが壊れ人件費が狂う）</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>列マッピングで吸収する（コードに列名を埋め込まない）</t>
+          <t>コード欠落／負値／未登録店舗／型不正／未定義の雇用区分をサーバ側で検証</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>T-I04 R-05</t>
+          <t>T-I05 R-03</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>§第2部 フロー1・8・9・10</t>
+          <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
         <is>
-          <t>T-I04.png</t>
+          <t>T-I05.png</t>
         </is>
       </c>
       <c r="N37" s="17" t="inlineStr"/>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない</t>
+          <t>入出力：CSが自走できる</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-24</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
@@ -2809,42 +2809,42 @@
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>異常が検出され、不正な値が登録されない</t>
+          <t>保存して再利用できる</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>4行すべて検出（見逃し=0）</t>
+          <t>保存済みテンプレート選択時の手入力=0項目。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>不可（マスタが壊れ人件費が狂う）</t>
+          <t>条件付きGo可（都度マッピングで代替）</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>コード欠落／負値／未登録店舗／型不正／未定義の雇用区分をサーバ側で検証</t>
+          <t>マッピングを保存・適用できる。開発なしで新形式に対応できる</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>T-I05 R-03</t>
+          <t>T-I09 R-05</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
+          <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>T-I05.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="N38" s="17" t="inlineStr"/>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>AC-24</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -2880,32 +2880,32 @@
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>保存して再利用できる</t>
+          <t>選んだ項目だけが出力される</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>保存済みテンプレート選択時の手入力=0項目。「全解除」で取込チェックが一括で外れる</t>
+          <t>出力の列＝チェックした項目（過不足=0列）</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（都度マッピングで代替）</t>
+          <t>不可（不要な給与情報が渡し先に漏れる）</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>マッピングを保存・適用できる。開発なしで新形式に対応できる</t>
+          <t>選択した列のみを生成する（固定フォーマットにしない）</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>T-I09 R-05</t>
+          <t>T-E04 T-E09</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="N39" s="17" t="inlineStr"/>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
+          <t>入出力：対象ごとに分ける</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-26</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>選んだ項目だけが出力される</t>
+          <t>対象ごとにファイルが分かれる</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>出力の列＝チェックした項目（過不足=0列）</t>
+          <t>ファイル数=2</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>不可（不要な給与情報が渡し先に漏れる）</t>
+          <t>条件付きGo可（手作業で分割）</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>選択した列のみを生成する（固定フォーマットにしない）</t>
+          <t>対象ごとにファイルを生成する</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>T-E04 T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>入出力：対象ごとに分ける</t>
+          <t>入出力：空振りを防ぐ</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>AC-26</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
@@ -3022,22 +3022,22 @@
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>対象ごとにファイルが分かれる</t>
+          <t>出力されず警告が出る</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>ファイル数=2</t>
+          <t>未選択での出力=0件</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（手作業で分割）</t>
+          <t>条件付きGo可</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>対象ごとにファイルを生成する</t>
+          <t>出力前に選択状態を検証する</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="N41" s="17" t="inlineStr"/>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：そのまま提出できる</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
@@ -3093,22 +3093,22 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>出力されず警告が出る</t>
+          <t>文字化けしない</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>未選択での出力=0件</t>
+          <t>文字化け=0箇所</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可</t>
+          <t>不可（外部提出に使えない）</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>出力前に選択状態を検証する</t>
+          <t>BOM付きUTF-8で出力する</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="N42" s="17" t="inlineStr"/>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
+          <t>画面：たどり着ける</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
@@ -3164,42 +3164,42 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>文字化けしない</t>
+          <t>2グループ7項目が表示される</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>文字化け=0箇所</t>
+          <t>欠落=0</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>不可（外部提出に使えない）</t>
+          <t>不可（画面に到達できない）</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>BOM付きUTF-8で出力する</t>
+          <t>閲覧・管理3／データ連携4でグループ化</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>サイドバー</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>§第2部 フロー1・8・9・10</t>
+          <t>§第1部 9 画面の構成 ／ 第2部 ケース別遷移</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="N43" s="17" t="inlineStr"/>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>画面：操作が最後まで通る</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
@@ -3235,32 +3235,32 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>2グループ7項目が表示される</t>
+          <t>仕様書 第2部の遷移どおりに画面が繋がる（取込データ⇄人件費実績の相互導線を含む）</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>欠落=0</t>
+          <t>不通=0</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>不可（画面に到達できない）</t>
+          <t>不可（フローが途中で切れる）</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>閲覧・管理3／データ連携4でグループ化</t>
+          <t>キャンセル・戻る・エラー時の遷移を含めて実装する</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>サイドバー</t>
+          <t>全画面</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-D08 T-E04 T-H04 T-I02 T-I09 T-L06 T-N03 T-R07 T-Z05</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-D08.png</t>
         </is>
       </c>
       <c r="N44" s="17" t="inlineStr"/>
@@ -3291,12 +3291,12 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>画面：対象を探せる</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-33</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
@@ -3306,32 +3306,32 @@
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>仕様書 第2部の遷移どおりに画面が繋がる（取込データ⇄人件費実績の相互導線を含む）</t>
+          <t>フィルタで対象を絞り込める</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>不通=0</t>
+          <t>各条件で絞り込みが効く（無反応=0）</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>不可（フローが途中で切れる）</t>
+          <t>条件付きGo可（件数が少ないうちは実害小）</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>キャンセル・戻る・エラー時の遷移を含めて実装する</t>
+          <t>1段目=絞り込み、2段目=対象データとして独立に効かせる</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>全画面</t>
+          <t>従業員一覧／設定履歴</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>T-D08 T-E04 T-H04 T-I02 T-I09 T-L06 T-N03 T-R07 T-Z05</t>
+          <t>T-H04 T-L08</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="M45" s="14" t="inlineStr">
         <is>
-          <t>T-D08.png</t>
+          <t>T-H04.png</t>
         </is>
       </c>
       <c r="N45" s="17" t="inlineStr"/>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>画面：対象を探せる</t>
+          <t>データ保全：消える操作は確認を経る</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>AC-33</t>
+          <t>AC-34</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
@@ -3377,42 +3377,42 @@
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>フィルタで対象を絞り込める</t>
+          <t>確認を経てのみ削除される</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>各条件で絞り込みが効く（無反応=0）</t>
+          <t>確認なしの削除=0件、キャンセル時の削除=0件</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（件数が少ないうちは実害小）</t>
+          <t>不可（誤操作で過去の紐付けが失われる）</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>1段目=絞り込み、2段目=対象データとして独立に効かせる</t>
+          <t>削除前に確認ダイアログ。キャンセルでリクエストを送らない</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>従業員一覧／設定履歴</t>
+          <t>従業員一覧／従業員詳細</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>T-H04 T-L08</t>
+          <t>T-D08 T-L10</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>§第1部 9 画面の構成 ／ 第2部 ケース別遷移</t>
+          <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-D08.png</t>
         </is>
       </c>
       <c r="N46" s="17" t="inlineStr"/>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>データ保全：消える操作は確認を経る</t>
+          <t>計算：個人単位でも同じ数字</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>AC-34</t>
+          <t>AC-35</t>
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr">
@@ -3448,42 +3448,42 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>確認を経てのみ削除される</t>
+          <t>画面が変わっても同じ数字が出る</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>確認なしの削除=0件、キャンセル時の削除=0件</t>
+          <t>同一従業員・同一月で差分=0円</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>不可（誤操作で過去の紐付けが失われる）</t>
+          <t>条件付きGo可（説明コストが増える）</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>削除前に確認ダイアログ。キャンセルでリクエストを送らない</t>
+          <t>同じ集計ロジックを共有する（画面ごとに別計算をしない）</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>従業員一覧／従業員詳細</t>
+          <t>従業員詳細（給与実績）</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>T-D08 T-L10</t>
+          <t>T-D09 R-04</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
+          <t>§第5部 11-A 確定した算式</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
-          <t>T-D08.png</t>
+          <t>T-D09.png</t>
         </is>
       </c>
       <c r="N47" s="17" t="inlineStr"/>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字</t>
+          <t>入出力：画面の内容と一致</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>AC-35</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
@@ -3519,42 +3519,42 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>画面が変わっても同じ数字が出る</t>
+          <t>表示中の内容どおりに出力される</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>同一従業員・同一月で差分=0円</t>
+          <t>出力の行・列＝画面の表示（差分0）</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（説明コストが増える）</t>
+          <t>条件付きGo可</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>同じ集計ロジックを共有する（画面ごとに別計算をしない）</t>
+          <t>出力は画面の絞り込み条件を引き継ぐ（全件出力にしない）</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>従業員詳細（給与実績）</t>
+          <t>人件費実績／設定履歴／従業員詳細</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>T-D09 R-04</t>
+          <t>T-A07 T-D09 T-H04</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>§第5部 11-A 確定した算式</t>
+          <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>T-D09.png</t>
+          <t>T-A07.png</t>
         </is>
       </c>
       <c r="N48" s="17" t="inlineStr"/>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>入出力：画面の内容と一致</t>
+          <t>入出力：現場のCSVをそのまま使える</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr">
@@ -3590,32 +3590,32 @@
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>表示中の内容どおりに出力される</t>
+          <t>開始行を指定すれば取り込める</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>出力の行・列＝画面の表示（差分0）</t>
+          <t>取込成功=全行</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可</t>
+          <t>条件付きGo可（顧客にCSV加工を依頼する運用で代替）</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>出力は画面の絞り込み条件を引き継ぐ（全件出力にしない）</t>
+          <t>ヘッダー行・データ開始行・開始列を指定できる</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>人件費実績／設定履歴／従業員詳細</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>T-A07 T-D09 T-H04</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="M49" s="14" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="N49" s="17" t="inlineStr"/>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
+          <t>入出力：原因を追える</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
@@ -3661,32 +3661,32 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>開始行を指定すれば取り込める</t>
+          <t>取り込んだ元データを確認できる</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>取込成功=全行</t>
+          <t>設定・実績とも参照可能</t>
         </is>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（顧客にCSV加工を依頼する運用で代替）</t>
+          <t>条件付きGo可（DBを直接見る運用で代替）</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>ヘッダー行・データ開始行・開始列を指定できる</t>
+          <t>取込ファイルと取込結果を保存し、画面から参照できる</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>設定取込データ／実績取込データ</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="N50" s="17" t="inlineStr"/>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
+          <t>データ保全：中途半端に残さない</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
@@ -3732,42 +3732,42 @@
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>取り込んだ元データを確認できる</t>
+          <t>途中で失敗しても中途半端な状態が残らない</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>設定・実績とも参照可能</t>
+          <t>部分登録の残存=0件</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>条件付きGo可（DBを直接見る運用で代替）</t>
+          <t>不可（どこまで入ったか分からず復旧できない）</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>取込ファイルと取込結果を保存し、画面から参照できる</t>
+          <t>全体をトランザクションで囲む（全体拒否）か、行単位で結果を明示する。どちらでも可だが挙動を固定する</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-I18 R-03</t>
         </is>
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
-          <t>§第2部 フロー1・8・9・10</t>
+          <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
       <c r="M51" s="14" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="N51" s="17" t="inlineStr"/>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
+          <t>データ保全：不完全な登録を作らない</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-43</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
@@ -3803,32 +3803,32 @@
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>途中で失敗しても中途半端な状態が残らない</t>
+          <t>必須が欠けたまま保存も遷移もしない</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>部分登録の残存=0件</t>
+          <t>未入力での登録成功=0件、遷移=0件</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>不可（どこまで入ったか分からず復旧できない）</t>
+          <t>不可（締め時に止まる従業員が生まれる）</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>全体をトランザクションで囲む（全体拒否）か、行単位で結果を明示する。どちらでも可だが挙動を固定する</t>
+          <t>サーバ側でも必須チェック（画面側だけにしない）。エラー時は同一画面に留まる</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>従業員登録</t>
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>T-I18 R-03</t>
+          <t>T-R10 R-03</t>
         </is>
       </c>
       <c r="L52" s="14" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-R10.png</t>
         </is>
       </c>
       <c r="N52" s="17" t="inlineStr"/>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>データ保全：不完全な登録を作らない</t>
+          <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>AC-43</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -3874,42 +3874,42 @@
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>必須が欠けたまま保存も遷移もしない</t>
+          <t>従業員詳細と人件費実績のモーダル、どちらから編集しても適用日付と履歴が同じ形式で残ること</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>未入力での登録成功=0件、遷移=0件</t>
+          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>不可（締め時に止まる従業員が生まれる）</t>
+          <t>不可（片方だけ履歴が残らないと変更を追えない期間ができ、AC-07・AC-03に連鎖）</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>サーバ側でも必須チェック（画面側だけにしない）。エラー時は同一画面に留まる</t>
+          <t>設定更新の処理を1箇所に集約し、両方の画面から同じ処理を呼ぶ。※この集約はM1（データ基盤）の時点で作る。後から画面ごとに分かれた実装を統合するのは困難。判定はモーダルが実装されるM4で行う</t>
         </is>
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>従業員登録</t>
+          <t>人件費実績（設定編集モーダル）／従業員詳細</t>
         </is>
       </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>T-R10 R-03</t>
+          <t>T-A09 R-06</t>
         </is>
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
-          <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
+          <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
       <c r="M53" s="14" t="inlineStr">
         <is>
-          <t>T-R10.png</t>
+          <t>T-A09.png</t>
         </is>
       </c>
       <c r="N53" s="17" t="inlineStr"/>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="L56" s="14" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="N56" s="17" t="inlineStr"/>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -2266,7 +2266,7 @@
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>C-008</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>C-008.png</t>
         </is>
       </c>
       <c r="N30" s="17" t="inlineStr"/>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認表'!$A$12:$Q$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$Q$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -205,7 +205,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -612,21 +611,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>従業員管理 受入条件 確認表 ─ 実装が合格ラインを満たすかを判定する</t>
+          <t>従業員管理 受入条件表 ─ どこまで実装できれば合格か</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>N列「合否」のプルダウンで OK / NG / 対象外 を選ぶと、上部の確認ステータスが自動更新されます。用語の定義は 20260805_従業員管理_00_定義表.xlsx、操作手順は 20260805_従業員管理_02_検証プラン.xlsx。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>■ 確認ステータス（下の合否を入れると自動で更新されます）</t>
+          <t>「合否」に OK / NG を入れると下の到達状況が自動更新されます。用語の定義は 20260805_従業員管理_00_定義表.xlsx、操作手順は 20260805_従業員管理_02_検証プラン.xlsx。</t>
         </is>
       </c>
     </row>
@@ -4629,11 +4621,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A12:Q63"/>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="B11:J11"/>
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="N13:N63">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$Q$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -600,12 +600,13 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,11 +683,11 @@
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A5,$N$13:$N$63,"OK")</f>
+        <f>COUNTIFS($A$13:$A$63,$A5,$O$13:$O$63,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A5,$N$13:$N$63,"NG")</f>
+        <f>COUNTIFS($A$13:$A$63,$A5,$O$13:$O$63,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="7">
@@ -720,11 +721,11 @@
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A6,$N$13:$N$63,"OK")</f>
+        <f>COUNTIFS($A$13:$A$63,$A6,$O$13:$O$63,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A6,$N$13:$N$63,"NG")</f>
+        <f>COUNTIFS($A$13:$A$63,$A6,$O$13:$O$63,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="7">
@@ -758,11 +759,11 @@
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A7,$N$13:$N$63,"OK")</f>
+        <f>COUNTIFS($A$13:$A$63,$A7,$O$13:$O$63,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A7,$N$13:$N$63,"NG")</f>
+        <f>COUNTIFS($A$13:$A$63,$A7,$O$13:$O$63,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="7">
@@ -796,11 +797,11 @@
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A8,$N$13:$N$63,"OK")</f>
+        <f>COUNTIFS($A$13:$A$63,$A8,$O$13:$O$63,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A8,$N$13:$N$63,"NG")</f>
+        <f>COUNTIFS($A$13:$A$63,$A8,$O$13:$O$63,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="7">
@@ -834,11 +835,11 @@
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A9,$N$13:$N$63,"OK")</f>
+        <f>COUNTIFS($A$13:$A$63,$A9,$O$13:$O$63,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A9,$N$13:$N$63,"NG")</f>
+        <f>COUNTIFS($A$13:$A$63,$A9,$O$13:$O$63,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="7">
@@ -872,11 +873,11 @@
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A10,$N$13:$N$63,"OK")</f>
+        <f>COUNTIFS($A$13:$A$63,$A10,$O$13:$O$63,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>COUNTIFS($A$13:$A$63,$A10,$N$13:$N$63,"NG")</f>
+        <f>COUNTIFS($A$13:$A$63,$A10,$O$13:$O$63,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="7">
@@ -899,7 +900,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>IF(COUNTIFS($E$13:$E$63,"L0*",$N$13:$N$63,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$63,"L1*",$N$13:$N$63,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$63,"L0*",$N$13:$N$63,"OK")+COUNTIFS($E$13:$E$63,"L1*",$N$13:$N$63,"OK")&lt;COUNTIF($E$13:$E$63,"L0*")+COUNTIF($E$13:$E$63,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$63,"L0*",$O$13:$O$63,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$63,"L1*",$O$13:$O$63,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$63,"L0*",$O$13:$O$63,"OK")+COUNTIFS($E$13:$E$63,"L1*",$O$13:$O$63,"OK")&lt;COUNTIF($E$13:$E$63,"L0*")+COUNTIF($E$13:$E$63,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
       <c r="C11" s="11" t="n"/>
@@ -969,30 +970,35 @@
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
+          <t>ヘルプページ該当箇所</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
           <t>仕様書の根拠</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr">
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t>エビデンス</t>
         </is>
       </c>
-      <c r="N12" s="13" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t>合否</t>
         </is>
       </c>
-      <c r="O12" s="13" t="inlineStr">
+      <c r="P12" s="13" t="inlineStr">
         <is>
           <t>実測値</t>
         </is>
       </c>
-      <c r="P12" s="13" t="inlineStr">
+      <c r="Q12" s="13" t="inlineStr">
         <is>
           <t>判定者</t>
         </is>
       </c>
-      <c r="Q12" s="13" t="inlineStr">
+      <c r="R12" s="13" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
@@ -1056,18 +1062,23 @@
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr">
+        <is>
           <t>§第4部 11 リリース段階 ／ 第7部 15 Go・No-Go</t>
         </is>
       </c>
-      <c r="M13" s="14" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t>T-Z02.png</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr"/>
-      <c r="O13" s="18" t="inlineStr"/>
-      <c r="P13" s="17" t="inlineStr"/>
+      <c r="O13" s="17" t="inlineStr"/>
+      <c r="P13" s="18" t="inlineStr"/>
       <c r="Q13" s="17" t="inlineStr"/>
+      <c r="R13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -1127,18 +1138,23 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr">
+      <c r="N14" s="14" t="inlineStr">
         <is>
           <t>T-D04.png</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr"/>
-      <c r="O14" s="18" t="inlineStr"/>
-      <c r="P14" s="17" t="inlineStr"/>
+      <c r="O14" s="17" t="inlineStr"/>
+      <c r="P14" s="18" t="inlineStr"/>
       <c r="Q14" s="17" t="inlineStr"/>
+      <c r="R14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1198,18 +1214,23 @@
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員を登録する ／ 操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="N15" s="14" t="inlineStr">
         <is>
           <t>T-D06.png</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr"/>
-      <c r="O15" s="18" t="inlineStr"/>
-      <c r="P15" s="17" t="inlineStr"/>
+      <c r="O15" s="17" t="inlineStr"/>
+      <c r="P15" s="18" t="inlineStr"/>
       <c r="Q15" s="17" t="inlineStr"/>
+      <c r="R15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -1269,18 +1290,23 @@
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員の設定を変更する ／ ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="N16" s="14" t="inlineStr">
         <is>
           <t>T-D01.png</t>
         </is>
       </c>
-      <c r="N16" s="17" t="inlineStr"/>
-      <c r="O16" s="18" t="inlineStr"/>
-      <c r="P16" s="17" t="inlineStr"/>
+      <c r="O16" s="17" t="inlineStr"/>
+      <c r="P16" s="18" t="inlineStr"/>
       <c r="Q16" s="17" t="inlineStr"/>
+      <c r="R16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -1340,18 +1366,23 @@
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M17" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>T-H02.png</t>
         </is>
       </c>
-      <c r="N17" s="17" t="inlineStr"/>
-      <c r="O17" s="18" t="inlineStr"/>
-      <c r="P17" s="17" t="inlineStr"/>
+      <c r="O17" s="17" t="inlineStr"/>
+      <c r="P17" s="18" t="inlineStr"/>
       <c r="Q17" s="17" t="inlineStr"/>
+      <c r="R17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -1411,18 +1442,23 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M18" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>T-H02.png</t>
         </is>
       </c>
-      <c r="N18" s="17" t="inlineStr"/>
-      <c r="O18" s="18" t="inlineStr"/>
-      <c r="P18" s="17" t="inlineStr"/>
+      <c r="O18" s="17" t="inlineStr"/>
+      <c r="P18" s="18" t="inlineStr"/>
       <c r="Q18" s="17" t="inlineStr"/>
+      <c r="R18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -1482,18 +1518,23 @@
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります ／ ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr">
+      <c r="N19" s="14" t="inlineStr">
         <is>
           <t>T-I17.png</t>
         </is>
       </c>
-      <c r="N19" s="17" t="inlineStr"/>
-      <c r="O19" s="18" t="inlineStr"/>
-      <c r="P19" s="17" t="inlineStr"/>
+      <c r="O19" s="17" t="inlineStr"/>
+      <c r="P19" s="18" t="inlineStr"/>
       <c r="Q19" s="17" t="inlineStr"/>
+      <c r="R19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -1553,18 +1594,23 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員を登録する ／ ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M20" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>T-R04.png</t>
         </is>
       </c>
-      <c r="N20" s="17" t="inlineStr"/>
-      <c r="O20" s="18" t="inlineStr"/>
-      <c r="P20" s="17" t="inlineStr"/>
+      <c r="O20" s="17" t="inlineStr"/>
+      <c r="P20" s="18" t="inlineStr"/>
       <c r="Q20" s="17" t="inlineStr"/>
+      <c r="R20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -1624,18 +1670,23 @@
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合 ／ 操作手順 ＞ 人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr">
+      <c r="N21" s="14" t="inlineStr">
         <is>
           <t>S-02.png</t>
         </is>
       </c>
-      <c r="N21" s="17" t="inlineStr"/>
-      <c r="O21" s="18" t="inlineStr"/>
-      <c r="P21" s="17" t="inlineStr"/>
+      <c r="O21" s="17" t="inlineStr"/>
+      <c r="P21" s="18" t="inlineStr"/>
       <c r="Q21" s="17" t="inlineStr"/>
+      <c r="R21" s="17" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -1695,18 +1746,23 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="M22" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
-      <c r="M22" s="14" t="inlineStr">
+      <c r="N22" s="14" t="inlineStr">
         <is>
           <t>T-D05.png</t>
         </is>
       </c>
-      <c r="N22" s="17" t="inlineStr"/>
-      <c r="O22" s="18" t="inlineStr"/>
-      <c r="P22" s="17" t="inlineStr"/>
+      <c r="O22" s="17" t="inlineStr"/>
+      <c r="P22" s="18" t="inlineStr"/>
       <c r="Q22" s="17" t="inlineStr"/>
+      <c r="R22" s="17" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -1766,18 +1822,23 @@
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する ／ 操作手順 ＞ 人件費の計算方法 ／ ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
           <t>§第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr">
+      <c r="N23" s="14" t="inlineStr">
         <is>
           <t>S-02.png</t>
         </is>
       </c>
-      <c r="N23" s="17" t="inlineStr"/>
-      <c r="O23" s="18" t="inlineStr"/>
-      <c r="P23" s="17" t="inlineStr"/>
+      <c r="O23" s="17" t="inlineStr"/>
+      <c r="P23" s="18" t="inlineStr"/>
       <c r="Q23" s="17" t="inlineStr"/>
+      <c r="R23" s="17" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -1837,18 +1898,23 @@
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
           <t>§第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr">
+      <c r="N24" s="14" t="inlineStr">
         <is>
           <t>S-02.png</t>
         </is>
       </c>
-      <c r="N24" s="17" t="inlineStr"/>
-      <c r="O24" s="18" t="inlineStr"/>
-      <c r="P24" s="17" t="inlineStr"/>
+      <c r="O24" s="17" t="inlineStr"/>
+      <c r="P24" s="18" t="inlineStr"/>
       <c r="Q24" s="17" t="inlineStr"/>
+      <c r="R24" s="17" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -1908,18 +1974,23 @@
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
           <t>§第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="N25" s="14" t="inlineStr">
         <is>
           <t>C-011.png</t>
         </is>
       </c>
-      <c r="N25" s="17" t="inlineStr"/>
-      <c r="O25" s="18" t="inlineStr"/>
-      <c r="P25" s="17" t="inlineStr"/>
+      <c r="O25" s="17" t="inlineStr"/>
+      <c r="P25" s="18" t="inlineStr"/>
       <c r="Q25" s="17" t="inlineStr"/>
+      <c r="R25" s="17" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -1979,18 +2050,23 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合 ／ 操作手順 ＞ 人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr">
+      <c r="N26" s="14" t="inlineStr">
         <is>
           <t>C-003.png</t>
         </is>
       </c>
-      <c r="N26" s="17" t="inlineStr"/>
-      <c r="O26" s="18" t="inlineStr"/>
-      <c r="P26" s="17" t="inlineStr"/>
+      <c r="O26" s="17" t="inlineStr"/>
+      <c r="P26" s="18" t="inlineStr"/>
       <c r="Q26" s="17" t="inlineStr"/>
+      <c r="R26" s="17" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -2050,18 +2126,23 @@
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員を登録する ／ ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則③ ／ 第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr">
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>S-02.png</t>
         </is>
       </c>
-      <c r="N27" s="17" t="inlineStr"/>
-      <c r="O27" s="18" t="inlineStr"/>
-      <c r="P27" s="17" t="inlineStr"/>
+      <c r="O27" s="17" t="inlineStr"/>
+      <c r="P27" s="18" t="inlineStr"/>
       <c r="Q27" s="17" t="inlineStr"/>
+      <c r="R27" s="17" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -2121,18 +2202,23 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M28" s="14" t="inlineStr">
+      <c r="N28" s="14" t="inlineStr">
         <is>
           <t>T-A08.png</t>
         </is>
       </c>
-      <c r="N28" s="17" t="inlineStr"/>
-      <c r="O28" s="18" t="inlineStr"/>
-      <c r="P28" s="17" t="inlineStr"/>
+      <c r="O28" s="17" t="inlineStr"/>
+      <c r="P28" s="18" t="inlineStr"/>
       <c r="Q28" s="17" t="inlineStr"/>
+      <c r="R28" s="17" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -2192,18 +2278,23 @@
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する ／ よくあるご質問 ＞ 数字・締めについて ／ よくあるご質問 ＞ どなたが操作できますか</t>
+        </is>
+      </c>
+      <c r="M29" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M29" s="14" t="inlineStr">
+      <c r="N29" s="14" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="N29" s="17" t="inlineStr"/>
-      <c r="O29" s="18" t="inlineStr"/>
-      <c r="P29" s="17" t="inlineStr"/>
+      <c r="O29" s="17" t="inlineStr"/>
+      <c r="P29" s="18" t="inlineStr"/>
       <c r="Q29" s="17" t="inlineStr"/>
+      <c r="R29" s="17" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -2263,18 +2354,23 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M30" s="14" t="inlineStr">
+      <c r="N30" s="14" t="inlineStr">
         <is>
           <t>C-008.png</t>
         </is>
       </c>
-      <c r="N30" s="17" t="inlineStr"/>
-      <c r="O30" s="18" t="inlineStr"/>
-      <c r="P30" s="17" t="inlineStr"/>
+      <c r="O30" s="17" t="inlineStr"/>
+      <c r="P30" s="18" t="inlineStr"/>
       <c r="Q30" s="17" t="inlineStr"/>
+      <c r="R30" s="17" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -2334,18 +2430,23 @@
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M31" s="14" t="inlineStr">
+      <c r="N31" s="14" t="inlineStr">
         <is>
           <t>T-S01.png</t>
         </is>
       </c>
-      <c r="N31" s="17" t="inlineStr"/>
-      <c r="O31" s="18" t="inlineStr"/>
-      <c r="P31" s="17" t="inlineStr"/>
+      <c r="O31" s="17" t="inlineStr"/>
+      <c r="P31" s="18" t="inlineStr"/>
       <c r="Q31" s="17" t="inlineStr"/>
+      <c r="R31" s="17" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -2405,18 +2506,23 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する ／ よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M32" s="14" t="inlineStr">
+      <c r="N32" s="14" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="N32" s="17" t="inlineStr"/>
-      <c r="O32" s="18" t="inlineStr"/>
-      <c r="P32" s="17" t="inlineStr"/>
+      <c r="O32" s="17" t="inlineStr"/>
+      <c r="P32" s="18" t="inlineStr"/>
       <c r="Q32" s="17" t="inlineStr"/>
+      <c r="R32" s="17" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -2476,18 +2582,23 @@
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
+      <c r="M33" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr">
+      <c r="N33" s="14" t="inlineStr">
         <is>
           <t>T-D07.png</t>
         </is>
       </c>
-      <c r="N33" s="17" t="inlineStr"/>
-      <c r="O33" s="18" t="inlineStr"/>
-      <c r="P33" s="17" t="inlineStr"/>
+      <c r="O33" s="17" t="inlineStr"/>
+      <c r="P33" s="18" t="inlineStr"/>
       <c r="Q33" s="17" t="inlineStr"/>
+      <c r="R33" s="17" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -2547,18 +2658,23 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr">
+      <c r="N34" s="14" t="inlineStr">
         <is>
           <t>T-S07.png</t>
         </is>
       </c>
-      <c r="N34" s="17" t="inlineStr"/>
-      <c r="O34" s="18" t="inlineStr"/>
-      <c r="P34" s="17" t="inlineStr"/>
+      <c r="O34" s="17" t="inlineStr"/>
+      <c r="P34" s="18" t="inlineStr"/>
       <c r="Q34" s="17" t="inlineStr"/>
+      <c r="R34" s="17" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -2618,18 +2734,23 @@
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ はじめて設定する</t>
+        </is>
+      </c>
+      <c r="M35" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M35" s="14" t="inlineStr">
+      <c r="N35" s="14" t="inlineStr">
         <is>
           <t>T-I02.png</t>
         </is>
       </c>
-      <c r="N35" s="17" t="inlineStr"/>
-      <c r="O35" s="18" t="inlineStr"/>
-      <c r="P35" s="17" t="inlineStr"/>
+      <c r="O35" s="17" t="inlineStr"/>
+      <c r="P35" s="18" t="inlineStr"/>
       <c r="Q35" s="17" t="inlineStr"/>
+      <c r="R35" s="17" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -2689,18 +2810,23 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ はじめて設定する ／ ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M36" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M36" s="14" t="inlineStr">
+      <c r="N36" s="14" t="inlineStr">
         <is>
           <t>T-I04.png</t>
         </is>
       </c>
-      <c r="N36" s="17" t="inlineStr"/>
-      <c r="O36" s="18" t="inlineStr"/>
-      <c r="P36" s="17" t="inlineStr"/>
+      <c r="O36" s="17" t="inlineStr"/>
+      <c r="P36" s="18" t="inlineStr"/>
       <c r="Q36" s="17" t="inlineStr"/>
+      <c r="R36" s="17" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -2760,18 +2886,23 @@
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります ／ よくあるご質問 ＞ 設定が保存できません</t>
+        </is>
+      </c>
+      <c r="M37" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
-      <c r="M37" s="14" t="inlineStr">
+      <c r="N37" s="14" t="inlineStr">
         <is>
           <t>T-I05.png</t>
         </is>
       </c>
-      <c r="N37" s="17" t="inlineStr"/>
-      <c r="O37" s="18" t="inlineStr"/>
-      <c r="P37" s="17" t="inlineStr"/>
+      <c r="O37" s="17" t="inlineStr"/>
+      <c r="P37" s="18" t="inlineStr"/>
       <c r="Q37" s="17" t="inlineStr"/>
+      <c r="R37" s="17" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -2831,18 +2962,23 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M38" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr">
+      <c r="N38" s="14" t="inlineStr">
         <is>
           <t>T-I09.png</t>
         </is>
       </c>
-      <c r="N38" s="17" t="inlineStr"/>
-      <c r="O38" s="18" t="inlineStr"/>
-      <c r="P38" s="17" t="inlineStr"/>
+      <c r="O38" s="17" t="inlineStr"/>
+      <c r="P38" s="18" t="inlineStr"/>
       <c r="Q38" s="17" t="inlineStr"/>
+      <c r="R38" s="17" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -2902,18 +3038,23 @@
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ データを出力する</t>
+        </is>
+      </c>
+      <c r="M39" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M39" s="14" t="inlineStr">
+      <c r="N39" s="14" t="inlineStr">
         <is>
           <t>T-E04.png</t>
         </is>
       </c>
-      <c r="N39" s="17" t="inlineStr"/>
-      <c r="O39" s="18" t="inlineStr"/>
-      <c r="P39" s="17" t="inlineStr"/>
+      <c r="O39" s="17" t="inlineStr"/>
+      <c r="P39" s="18" t="inlineStr"/>
       <c r="Q39" s="17" t="inlineStr"/>
+      <c r="R39" s="17" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -2973,18 +3114,23 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ データを出力する</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M40" s="14" t="inlineStr">
+      <c r="N40" s="14" t="inlineStr">
         <is>
           <t>T-E04.png</t>
         </is>
       </c>
-      <c r="N40" s="17" t="inlineStr"/>
-      <c r="O40" s="18" t="inlineStr"/>
-      <c r="P40" s="17" t="inlineStr"/>
+      <c r="O40" s="17" t="inlineStr"/>
+      <c r="P40" s="18" t="inlineStr"/>
       <c r="Q40" s="17" t="inlineStr"/>
+      <c r="R40" s="17" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -3044,18 +3190,23 @@
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ データを出力する</t>
+        </is>
+      </c>
+      <c r="M41" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M41" s="14" t="inlineStr">
+      <c r="N41" s="14" t="inlineStr">
         <is>
           <t>T-E07.png</t>
         </is>
       </c>
-      <c r="N41" s="17" t="inlineStr"/>
-      <c r="O41" s="18" t="inlineStr"/>
-      <c r="P41" s="17" t="inlineStr"/>
+      <c r="O41" s="17" t="inlineStr"/>
+      <c r="P41" s="18" t="inlineStr"/>
       <c r="Q41" s="17" t="inlineStr"/>
+      <c r="R41" s="17" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -3115,18 +3266,23 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ データを出力する</t>
+        </is>
+      </c>
+      <c r="M42" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M42" s="14" t="inlineStr">
+      <c r="N42" s="14" t="inlineStr">
         <is>
           <t>T-E08.png</t>
         </is>
       </c>
-      <c r="N42" s="17" t="inlineStr"/>
-      <c r="O42" s="18" t="inlineStr"/>
-      <c r="P42" s="17" t="inlineStr"/>
+      <c r="O42" s="17" t="inlineStr"/>
+      <c r="P42" s="18" t="inlineStr"/>
       <c r="Q42" s="17" t="inlineStr"/>
+      <c r="R42" s="17" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -3184,20 +3340,21 @@
           <t>T-Z04</t>
         </is>
       </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="L43" s="14" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr">
         <is>
           <t>§第1部 9 画面の構成 ／ 第2部 ケース別遷移</t>
         </is>
       </c>
-      <c r="M43" s="14" t="inlineStr">
+      <c r="N43" s="14" t="inlineStr">
         <is>
           <t>T-Z04.png</t>
         </is>
       </c>
-      <c r="N43" s="17" t="inlineStr"/>
-      <c r="O43" s="18" t="inlineStr"/>
-      <c r="P43" s="17" t="inlineStr"/>
+      <c r="O43" s="17" t="inlineStr"/>
+      <c r="P43" s="18" t="inlineStr"/>
       <c r="Q43" s="17" t="inlineStr"/>
+      <c r="R43" s="17" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -3257,18 +3414,23 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員を探す・削除する ／ 操作手順 ＞ 従業員を登録する ／ ケース別 ＞ 数字が合わないとき ／ 操作手順 ＞ はじめて設定する ／ ケース別 ＞ CSVの列名がラクミーと違うとき ／ 操作手順 ＞ データを出力する ／ 操作手順 ＞ 取り込んだ元データを確認する</t>
+        </is>
+      </c>
+      <c r="M44" s="14" t="inlineStr">
+        <is>
           <t>§第1部 9 画面の構成 ／ 第2部 ケース別遷移</t>
         </is>
       </c>
-      <c r="M44" s="14" t="inlineStr">
+      <c r="N44" s="14" t="inlineStr">
         <is>
           <t>T-D08.png</t>
         </is>
       </c>
-      <c r="N44" s="17" t="inlineStr"/>
-      <c r="O44" s="18" t="inlineStr"/>
-      <c r="P44" s="17" t="inlineStr"/>
+      <c r="O44" s="17" t="inlineStr"/>
+      <c r="P44" s="18" t="inlineStr"/>
       <c r="Q44" s="17" t="inlineStr"/>
+      <c r="R44" s="17" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -3328,18 +3490,23 @@
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員を探す・削除する ／ ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M45" s="14" t="inlineStr">
+        <is>
           <t>§第1部 9 画面の構成 ／ 第2部 ケース別遷移</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr">
+      <c r="N45" s="14" t="inlineStr">
         <is>
           <t>T-H04.png</t>
         </is>
       </c>
-      <c r="N45" s="17" t="inlineStr"/>
-      <c r="O45" s="18" t="inlineStr"/>
-      <c r="P45" s="17" t="inlineStr"/>
+      <c r="O45" s="17" t="inlineStr"/>
+      <c r="P45" s="18" t="inlineStr"/>
       <c r="Q45" s="17" t="inlineStr"/>
+      <c r="R45" s="17" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -3399,18 +3566,23 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
+        </is>
+      </c>
+      <c r="M46" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
-      <c r="M46" s="14" t="inlineStr">
+      <c r="N46" s="14" t="inlineStr">
         <is>
           <t>T-D08.png</t>
         </is>
       </c>
-      <c r="N46" s="17" t="inlineStr"/>
-      <c r="O46" s="18" t="inlineStr"/>
-      <c r="P46" s="17" t="inlineStr"/>
+      <c r="O46" s="17" t="inlineStr"/>
+      <c r="P46" s="18" t="inlineStr"/>
       <c r="Q46" s="17" t="inlineStr"/>
+      <c r="R46" s="17" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -3470,18 +3642,23 @@
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する ／ 操作手順 ＞ 人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="M47" s="14" t="inlineStr">
+        <is>
           <t>§第5部 11-A 確定した算式</t>
         </is>
       </c>
-      <c r="M47" s="14" t="inlineStr">
+      <c r="N47" s="14" t="inlineStr">
         <is>
           <t>T-D09.png</t>
         </is>
       </c>
-      <c r="N47" s="17" t="inlineStr"/>
-      <c r="O47" s="18" t="inlineStr"/>
-      <c r="P47" s="17" t="inlineStr"/>
+      <c r="O47" s="17" t="inlineStr"/>
+      <c r="P47" s="18" t="inlineStr"/>
       <c r="Q47" s="17" t="inlineStr"/>
+      <c r="R47" s="17" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -3541,18 +3718,23 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する ／ ケース別 ＞ 数字が合わないとき ／ 操作手順 ＞ データを出力する</t>
+        </is>
+      </c>
+      <c r="M48" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M48" s="14" t="inlineStr">
+      <c r="N48" s="14" t="inlineStr">
         <is>
           <t>T-A07.png</t>
         </is>
       </c>
-      <c r="N48" s="17" t="inlineStr"/>
-      <c r="O48" s="18" t="inlineStr"/>
-      <c r="P48" s="17" t="inlineStr"/>
+      <c r="O48" s="17" t="inlineStr"/>
+      <c r="P48" s="18" t="inlineStr"/>
       <c r="Q48" s="17" t="inlineStr"/>
+      <c r="R48" s="17" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -3612,18 +3794,23 @@
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M49" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M49" s="14" t="inlineStr">
+      <c r="N49" s="14" t="inlineStr">
         <is>
           <t>T-I11.png</t>
         </is>
       </c>
-      <c r="N49" s="17" t="inlineStr"/>
-      <c r="O49" s="18" t="inlineStr"/>
-      <c r="P49" s="17" t="inlineStr"/>
+      <c r="O49" s="17" t="inlineStr"/>
+      <c r="P49" s="18" t="inlineStr"/>
       <c r="Q49" s="17" t="inlineStr"/>
+      <c r="R49" s="17" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
@@ -3683,18 +3870,23 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+        </is>
+      </c>
+      <c r="M50" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M50" s="14" t="inlineStr">
+      <c r="N50" s="14" t="inlineStr">
         <is>
           <t>T-N01.png</t>
         </is>
       </c>
-      <c r="N50" s="17" t="inlineStr"/>
-      <c r="O50" s="18" t="inlineStr"/>
-      <c r="P50" s="17" t="inlineStr"/>
+      <c r="O50" s="17" t="inlineStr"/>
+      <c r="P50" s="18" t="inlineStr"/>
       <c r="Q50" s="17" t="inlineStr"/>
+      <c r="R50" s="17" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -3754,18 +3946,23 @@
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります ／ よくあるご質問 ＞ 設定が保存できません</t>
+        </is>
+      </c>
+      <c r="M51" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
-      <c r="M51" s="14" t="inlineStr">
+      <c r="N51" s="14" t="inlineStr">
         <is>
           <t>T-I18.png</t>
         </is>
       </c>
-      <c r="N51" s="17" t="inlineStr"/>
-      <c r="O51" s="18" t="inlineStr"/>
-      <c r="P51" s="17" t="inlineStr"/>
+      <c r="O51" s="17" t="inlineStr"/>
+      <c r="P51" s="18" t="inlineStr"/>
       <c r="Q51" s="17" t="inlineStr"/>
+      <c r="R51" s="17" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
@@ -3825,18 +4022,23 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
+        </is>
+      </c>
+      <c r="M52" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
-      <c r="M52" s="14" t="inlineStr">
+      <c r="N52" s="14" t="inlineStr">
         <is>
           <t>T-R10.png</t>
         </is>
       </c>
-      <c r="N52" s="17" t="inlineStr"/>
-      <c r="O52" s="18" t="inlineStr"/>
-      <c r="P52" s="17" t="inlineStr"/>
+      <c r="O52" s="17" t="inlineStr"/>
+      <c r="P52" s="18" t="inlineStr"/>
       <c r="Q52" s="17" t="inlineStr"/>
+      <c r="R52" s="17" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -3896,18 +4098,23 @@
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M53" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則① ／ 第2部 フロー3・4</t>
         </is>
       </c>
-      <c r="M53" s="14" t="inlineStr">
+      <c r="N53" s="14" t="inlineStr">
         <is>
           <t>T-A09.png</t>
         </is>
       </c>
-      <c r="N53" s="17" t="inlineStr"/>
-      <c r="O53" s="18" t="inlineStr"/>
-      <c r="P53" s="17" t="inlineStr"/>
+      <c r="O53" s="17" t="inlineStr"/>
+      <c r="P53" s="18" t="inlineStr"/>
       <c r="Q53" s="17" t="inlineStr"/>
+      <c r="R53" s="17" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
@@ -3967,18 +4174,23 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+        </is>
+      </c>
+      <c r="M54" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
-      <c r="M54" s="14" t="inlineStr">
+      <c r="N54" s="14" t="inlineStr">
         <is>
           <t>T-N02.png</t>
         </is>
       </c>
-      <c r="N54" s="17" t="inlineStr"/>
-      <c r="O54" s="18" t="inlineStr"/>
-      <c r="P54" s="17" t="inlineStr"/>
+      <c r="O54" s="17" t="inlineStr"/>
+      <c r="P54" s="18" t="inlineStr"/>
       <c r="Q54" s="17" t="inlineStr"/>
+      <c r="R54" s="17" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -4038,18 +4250,23 @@
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 従業員を探す・削除する ／ ケース別 ＞ すでにご利用中のお客様</t>
+        </is>
+      </c>
+      <c r="M55" s="14" t="inlineStr">
+        <is>
           <t>§第4部 11 リリース段階 ／ 第7部 15 Go・No-Go</t>
         </is>
       </c>
-      <c r="M55" s="14" t="inlineStr">
+      <c r="N55" s="14" t="inlineStr">
         <is>
           <t>T-L01.png</t>
         </is>
       </c>
-      <c r="N55" s="17" t="inlineStr"/>
-      <c r="O55" s="18" t="inlineStr"/>
-      <c r="P55" s="17" t="inlineStr"/>
+      <c r="O55" s="17" t="inlineStr"/>
+      <c r="P55" s="18" t="inlineStr"/>
       <c r="Q55" s="17" t="inlineStr"/>
+      <c r="R55" s="17" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
@@ -4109,18 +4326,23 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
+        </is>
+      </c>
+      <c r="M56" s="14" t="inlineStr">
+        <is>
           <t>§第4部 11 リリース段階 ／ 第7部 15 Go・No-Go</t>
         </is>
       </c>
-      <c r="M56" s="14" t="inlineStr">
+      <c r="N56" s="14" t="inlineStr">
         <is>
           <t>T-Z03.png</t>
         </is>
       </c>
-      <c r="N56" s="17" t="inlineStr"/>
-      <c r="O56" s="18" t="inlineStr"/>
-      <c r="P56" s="17" t="inlineStr"/>
+      <c r="O56" s="17" t="inlineStr"/>
+      <c r="P56" s="18" t="inlineStr"/>
       <c r="Q56" s="17" t="inlineStr"/>
+      <c r="R56" s="17" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
@@ -4180,18 +4402,23 @@
       </c>
       <c r="L57" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M57" s="14" t="inlineStr">
+        <is>
           <t>§第1部 9 画面の構成 ／ 第2部 ケース別遷移</t>
         </is>
       </c>
-      <c r="M57" s="14" t="inlineStr">
+      <c r="N57" s="14" t="inlineStr">
         <is>
           <t>T-A02.png</t>
         </is>
       </c>
-      <c r="N57" s="17" t="inlineStr"/>
-      <c r="O57" s="18" t="inlineStr"/>
-      <c r="P57" s="17" t="inlineStr"/>
+      <c r="O57" s="17" t="inlineStr"/>
+      <c r="P57" s="18" t="inlineStr"/>
       <c r="Q57" s="17" t="inlineStr"/>
+      <c r="R57" s="17" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
@@ -4251,18 +4478,23 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="inlineStr">
+        <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M58" s="14" t="inlineStr">
+      <c r="N58" s="14" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="N58" s="17" t="inlineStr"/>
-      <c r="O58" s="18" t="inlineStr"/>
-      <c r="P58" s="17" t="inlineStr"/>
+      <c r="O58" s="17" t="inlineStr"/>
+      <c r="P58" s="18" t="inlineStr"/>
       <c r="Q58" s="17" t="inlineStr"/>
+      <c r="R58" s="17" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
@@ -4322,18 +4554,23 @@
       </c>
       <c r="L59" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M59" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M59" s="14" t="inlineStr">
+      <c r="N59" s="14" t="inlineStr">
         <is>
           <t>T-I09.png</t>
         </is>
       </c>
-      <c r="N59" s="17" t="inlineStr"/>
-      <c r="O59" s="18" t="inlineStr"/>
-      <c r="P59" s="17" t="inlineStr"/>
+      <c r="O59" s="17" t="inlineStr"/>
+      <c r="P59" s="18" t="inlineStr"/>
       <c r="Q59" s="17" t="inlineStr"/>
+      <c r="R59" s="17" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -4391,20 +4628,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L60" s="14" t="inlineStr">
+      <c r="L60" s="14" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr">
         <is>
           <t>§第2部 フロー1・2 ／ 第5部 判断9</t>
         </is>
       </c>
-      <c r="M60" s="14" t="inlineStr">
+      <c r="N60" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N60" s="17" t="inlineStr"/>
-      <c r="O60" s="18" t="inlineStr"/>
-      <c r="P60" s="17" t="inlineStr"/>
+      <c r="O60" s="17" t="inlineStr"/>
+      <c r="P60" s="18" t="inlineStr"/>
       <c r="Q60" s="17" t="inlineStr"/>
+      <c r="R60" s="17" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
@@ -4462,20 +4700,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L61" s="14" t="inlineStr">
+      <c r="L61" s="14" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr">
         <is>
           <t>§第1部 7 原則② ／ 第2部 フロー6・7</t>
         </is>
       </c>
-      <c r="M61" s="14" t="inlineStr">
+      <c r="N61" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N61" s="17" t="inlineStr"/>
-      <c r="O61" s="18" t="inlineStr"/>
-      <c r="P61" s="17" t="inlineStr"/>
+      <c r="O61" s="17" t="inlineStr"/>
+      <c r="P61" s="18" t="inlineStr"/>
       <c r="Q61" s="17" t="inlineStr"/>
+      <c r="R61" s="17" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
@@ -4533,20 +4772,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L62" s="14" t="inlineStr">
+      <c r="L62" s="14" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr">
         <is>
           <t>§第1部 9 画面の構成 ／ 第2部 ケース別遷移</t>
         </is>
       </c>
-      <c r="M62" s="14" t="inlineStr">
+      <c r="N62" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N62" s="17" t="inlineStr"/>
-      <c r="O62" s="18" t="inlineStr"/>
-      <c r="P62" s="17" t="inlineStr"/>
+      <c r="O62" s="17" t="inlineStr"/>
+      <c r="P62" s="18" t="inlineStr"/>
       <c r="Q62" s="17" t="inlineStr"/>
+      <c r="R62" s="17" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
@@ -4606,27 +4846,32 @@
       </c>
       <c r="L63" s="14" t="inlineStr">
         <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M63" s="14" t="inlineStr">
+        <is>
           <t>§第2部 フロー1・8・9・10</t>
         </is>
       </c>
-      <c r="M63" s="14" t="inlineStr">
+      <c r="N63" s="14" t="inlineStr">
         <is>
           <t>T-I19.png</t>
         </is>
       </c>
-      <c r="N63" s="17" t="inlineStr"/>
-      <c r="O63" s="18" t="inlineStr"/>
-      <c r="P63" s="17" t="inlineStr"/>
+      <c r="O63" s="17" t="inlineStr"/>
+      <c r="P63" s="18" t="inlineStr"/>
       <c r="Q63" s="17" t="inlineStr"/>
+      <c r="R63" s="17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A12:Q63"/>
+  <autoFilter ref="A12:R63"/>
   <mergeCells count="3">
-    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
-    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="N13:N63">
+  <conditionalFormatting sqref="O13:O63">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4643,7 +4888,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N13:N63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -1004,7 +1004,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="49" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1080,7 +1080,7 @@
       <c r="Q13" s="17" t="inlineStr"/>
       <c r="R13" s="17" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" ht="49" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1156,7 +1156,7 @@
       <c r="Q14" s="17" t="inlineStr"/>
       <c r="R14" s="17" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="49" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>T-D06 T-R02 T-R07</t>
+          <t>T-R02 T-R07 T-D06</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
-          <t>T-D06.png</t>
+          <t>T-R02.png</t>
         </is>
       </c>
       <c r="O15" s="17" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       <c r="Q15" s="17" t="inlineStr"/>
       <c r="R15" s="17" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="49" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1308,7 +1308,7 @@
       <c r="Q16" s="17" t="inlineStr"/>
       <c r="R16" s="17" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="49" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1384,7 +1384,7 @@
       <c r="Q17" s="17" t="inlineStr"/>
       <c r="R17" s="17" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="49" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1460,7 +1460,7 @@
       <c r="Q18" s="17" t="inlineStr"/>
       <c r="R18" s="17" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" ht="49" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1536,7 +1536,7 @@
       <c r="Q19" s="17" t="inlineStr"/>
       <c r="R19" s="17" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="20" ht="49" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1612,7 +1612,7 @@
       <c r="Q20" s="17" t="inlineStr"/>
       <c r="R20" s="17" t="inlineStr"/>
     </row>
-    <row r="21">
+    <row r="21" ht="64" customHeight="1">
       <c r="A21" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -1688,7 +1688,7 @@
       <c r="Q21" s="17" t="inlineStr"/>
       <c r="R21" s="17" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" ht="49" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -1764,7 +1764,7 @@
       <c r="Q22" s="17" t="inlineStr"/>
       <c r="R22" s="17" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="23" ht="64" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -1840,7 +1840,7 @@
       <c r="Q23" s="17" t="inlineStr"/>
       <c r="R23" s="17" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" ht="49" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -1916,7 +1916,7 @@
       <c r="Q24" s="17" t="inlineStr"/>
       <c r="R24" s="17" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="49" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -1992,7 +1992,7 @@
       <c r="Q25" s="17" t="inlineStr"/>
       <c r="R25" s="17" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="26" ht="49" customHeight="1">
       <c r="A26" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -2068,7 +2068,7 @@
       <c r="Q26" s="17" t="inlineStr"/>
       <c r="R26" s="17" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" ht="49" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -2144,7 +2144,7 @@
       <c r="Q27" s="17" t="inlineStr"/>
       <c r="R27" s="17" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" ht="49" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -2220,7 +2220,7 @@
       <c r="Q28" s="17" t="inlineStr"/>
       <c r="R28" s="17" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="29" ht="79" customHeight="1">
       <c r="A29" s="14" t="inlineStr">
         <is>
           <t>M3 月次を確定して外部へ渡せる</t>
@@ -2296,7 +2296,7 @@
       <c r="Q29" s="17" t="inlineStr"/>
       <c r="R29" s="17" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="49" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
           <t>M3 月次を確定して外部へ渡せる</t>
@@ -2372,7 +2372,7 @@
       <c r="Q30" s="17" t="inlineStr"/>
       <c r="R30" s="17" t="inlineStr"/>
     </row>
-    <row r="31">
+    <row r="31" ht="49" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
           <t>M3 月次を確定して外部へ渡せる</t>
@@ -2448,7 +2448,7 @@
       <c r="Q31" s="17" t="inlineStr"/>
       <c r="R31" s="17" t="inlineStr"/>
     </row>
-    <row r="32">
+    <row r="32" ht="49" customHeight="1">
       <c r="A32" s="14" t="inlineStr">
         <is>
           <t>M3 月次を確定して外部へ渡せる</t>
@@ -2524,7 +2524,7 @@
       <c r="Q32" s="17" t="inlineStr"/>
       <c r="R32" s="17" t="inlineStr"/>
     </row>
-    <row r="33">
+    <row r="33" ht="49" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
         <is>
           <t>M3 月次を確定して外部へ渡せる</t>
@@ -2600,7 +2600,7 @@
       <c r="Q33" s="17" t="inlineStr"/>
       <c r="R33" s="17" t="inlineStr"/>
     </row>
-    <row r="34">
+    <row r="34" ht="49" customHeight="1">
       <c r="A34" s="14" t="inlineStr">
         <is>
           <t>M3 月次を確定して外部へ渡せる</t>
@@ -2676,7 +2676,7 @@
       <c r="Q34" s="17" t="inlineStr"/>
       <c r="R34" s="17" t="inlineStr"/>
     </row>
-    <row r="35">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -2752,7 +2752,7 @@
       <c r="Q35" s="17" t="inlineStr"/>
       <c r="R35" s="17" t="inlineStr"/>
     </row>
-    <row r="36">
+    <row r="36" ht="49" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -2828,7 +2828,7 @@
       <c r="Q36" s="17" t="inlineStr"/>
       <c r="R36" s="17" t="inlineStr"/>
     </row>
-    <row r="37">
+    <row r="37" ht="64" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -2904,7 +2904,7 @@
       <c r="Q37" s="17" t="inlineStr"/>
       <c r="R37" s="17" t="inlineStr"/>
     </row>
-    <row r="38">
+    <row r="38" ht="34" customHeight="1">
       <c r="A38" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -2980,7 +2980,7 @@
       <c r="Q38" s="17" t="inlineStr"/>
       <c r="R38" s="17" t="inlineStr"/>
     </row>
-    <row r="39">
+    <row r="39" ht="34" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3056,7 +3056,7 @@
       <c r="Q39" s="17" t="inlineStr"/>
       <c r="R39" s="17" t="inlineStr"/>
     </row>
-    <row r="40">
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3132,7 +3132,7 @@
       <c r="Q40" s="17" t="inlineStr"/>
       <c r="R40" s="17" t="inlineStr"/>
     </row>
-    <row r="41">
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3208,7 +3208,7 @@
       <c r="Q41" s="17" t="inlineStr"/>
       <c r="R41" s="17" t="inlineStr"/>
     </row>
-    <row r="42">
+    <row r="42" ht="34" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3284,7 +3284,7 @@
       <c r="Q42" s="17" t="inlineStr"/>
       <c r="R42" s="17" t="inlineStr"/>
     </row>
-    <row r="43">
+    <row r="43" ht="34" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3356,7 +3356,7 @@
       <c r="Q43" s="17" t="inlineStr"/>
       <c r="R43" s="17" t="inlineStr"/>
     </row>
-    <row r="44">
+    <row r="44" ht="154" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>T-D08 T-E04 T-H04 T-I02 T-I09 T-L06 T-N03 T-R07 T-Z05</t>
+          <t>T-L06 T-R07 T-D08 T-H04 T-I02 T-I09 T-E04 T-N03 T-Z05</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="N44" s="14" t="inlineStr">
         <is>
-          <t>T-D08.png</t>
+          <t>T-L06.png</t>
         </is>
       </c>
       <c r="O44" s="17" t="inlineStr"/>
@@ -3432,7 +3432,7 @@
       <c r="Q44" s="17" t="inlineStr"/>
       <c r="R44" s="17" t="inlineStr"/>
     </row>
-    <row r="45">
+    <row r="45" ht="49" customHeight="1">
       <c r="A45" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>T-H04 T-L08</t>
+          <t>T-L08 T-H04</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-L08.png</t>
         </is>
       </c>
       <c r="O45" s="17" t="inlineStr"/>
@@ -3508,7 +3508,7 @@
       <c r="Q45" s="17" t="inlineStr"/>
       <c r="R45" s="17" t="inlineStr"/>
     </row>
-    <row r="46">
+    <row r="46" ht="34" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>T-D08 T-L10</t>
+          <t>T-L10 T-D08</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="N46" s="14" t="inlineStr">
         <is>
-          <t>T-D08.png</t>
+          <t>T-L10.png</t>
         </is>
       </c>
       <c r="O46" s="17" t="inlineStr"/>
@@ -3584,7 +3584,7 @@
       <c r="Q46" s="17" t="inlineStr"/>
       <c r="R46" s="17" t="inlineStr"/>
     </row>
-    <row r="47">
+    <row r="47" ht="49" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3660,7 +3660,7 @@
       <c r="Q47" s="17" t="inlineStr"/>
       <c r="R47" s="17" t="inlineStr"/>
     </row>
-    <row r="48">
+    <row r="48" ht="64" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>T-A07 T-D09 T-H04</t>
+          <t>T-D09 T-H04 T-A07</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="N48" s="14" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-D09.png</t>
         </is>
       </c>
       <c r="O48" s="17" t="inlineStr"/>
@@ -3736,7 +3736,7 @@
       <c r="Q48" s="17" t="inlineStr"/>
       <c r="R48" s="17" t="inlineStr"/>
     </row>
-    <row r="49">
+    <row r="49" ht="34" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3812,7 +3812,7 @@
       <c r="Q49" s="17" t="inlineStr"/>
       <c r="R49" s="17" t="inlineStr"/>
     </row>
-    <row r="50">
+    <row r="50" ht="34" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3888,7 +3888,7 @@
       <c r="Q50" s="17" t="inlineStr"/>
       <c r="R50" s="17" t="inlineStr"/>
     </row>
-    <row r="51">
+    <row r="51" ht="64" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3964,7 +3964,7 @@
       <c r="Q51" s="17" t="inlineStr"/>
       <c r="R51" s="17" t="inlineStr"/>
     </row>
-    <row r="52">
+    <row r="52" ht="49" customHeight="1">
       <c r="A52" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4040,7 +4040,7 @@
       <c r="Q52" s="17" t="inlineStr"/>
       <c r="R52" s="17" t="inlineStr"/>
     </row>
-    <row r="53">
+    <row r="53" ht="94" customHeight="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4116,7 +4116,7 @@
       <c r="Q53" s="17" t="inlineStr"/>
       <c r="R53" s="17" t="inlineStr"/>
     </row>
-    <row r="54">
+    <row r="54" ht="49" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4192,7 +4192,7 @@
       <c r="Q54" s="17" t="inlineStr"/>
       <c r="R54" s="17" t="inlineStr"/>
     </row>
-    <row r="55">
+    <row r="55" ht="49" customHeight="1">
       <c r="A55" s="14" t="inlineStr">
         <is>
           <t>M5 既存顧客を壊さない</t>
@@ -4268,7 +4268,7 @@
       <c r="Q55" s="17" t="inlineStr"/>
       <c r="R55" s="17" t="inlineStr"/>
     </row>
-    <row r="56">
+    <row r="56" ht="49" customHeight="1">
       <c r="A56" s="14" t="inlineStr">
         <is>
           <t>M5 既存顧客を壊さない</t>
@@ -4344,7 +4344,7 @@
       <c r="Q56" s="17" t="inlineStr"/>
       <c r="R56" s="17" t="inlineStr"/>
     </row>
-    <row r="57">
+    <row r="57" ht="34" customHeight="1">
       <c r="A57" s="14" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>
@@ -4420,7 +4420,7 @@
       <c r="Q57" s="17" t="inlineStr"/>
       <c r="R57" s="17" t="inlineStr"/>
     </row>
-    <row r="58">
+    <row r="58" ht="49" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>
@@ -4496,7 +4496,7 @@
       <c r="Q58" s="17" t="inlineStr"/>
       <c r="R58" s="17" t="inlineStr"/>
     </row>
-    <row r="59">
+    <row r="59" ht="34" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>
@@ -4572,7 +4572,7 @@
       <c r="Q59" s="17" t="inlineStr"/>
       <c r="R59" s="17" t="inlineStr"/>
     </row>
-    <row r="60">
+    <row r="60" ht="34" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>
@@ -4644,7 +4644,7 @@
       <c r="Q60" s="17" t="inlineStr"/>
       <c r="R60" s="17" t="inlineStr"/>
     </row>
-    <row r="61">
+    <row r="61" ht="34" customHeight="1">
       <c r="A61" s="14" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>
@@ -4716,7 +4716,7 @@
       <c r="Q61" s="17" t="inlineStr"/>
       <c r="R61" s="17" t="inlineStr"/>
     </row>
-    <row r="62">
+    <row r="62" ht="34" customHeight="1">
       <c r="A62" s="14" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>
@@ -4788,7 +4788,7 @@
       <c r="Q62" s="17" t="inlineStr"/>
       <c r="R62" s="17" t="inlineStr"/>
     </row>
-    <row r="63">
+    <row r="63" ht="64" customHeight="1">
       <c r="A63" s="14" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$65,$A5)</f>
+        <f>COUNTIF($A$13:$A$66,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A5,$O$13:$O$65,"OK")</f>
+        <f>COUNTIFS($A$13:$A$66,$A5,$O$13:$O$66,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A5,$O$13:$O$65,"NG")</f>
+        <f>COUNTIFS($A$13:$A$66,$A5,$O$13:$O$66,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$65,$A6)</f>
+        <f>COUNTIF($A$13:$A$66,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A6,$O$13:$O$65,"OK")</f>
+        <f>COUNTIFS($A$13:$A$66,$A6,$O$13:$O$66,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A6,$O$13:$O$65,"NG")</f>
+        <f>COUNTIFS($A$13:$A$66,$A6,$O$13:$O$66,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$65,$A7)</f>
+        <f>COUNTIF($A$13:$A$66,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A7,$O$13:$O$65,"OK")</f>
+        <f>COUNTIFS($A$13:$A$66,$A7,$O$13:$O$66,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A7,$O$13:$O$65,"NG")</f>
+        <f>COUNTIFS($A$13:$A$66,$A7,$O$13:$O$66,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$65,$A8)</f>
+        <f>COUNTIF($A$13:$A$66,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A8,$O$13:$O$65,"OK")</f>
+        <f>COUNTIFS($A$13:$A$66,$A8,$O$13:$O$66,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A8,$O$13:$O$65,"NG")</f>
+        <f>COUNTIFS($A$13:$A$66,$A8,$O$13:$O$66,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$65,$A9)</f>
+        <f>COUNTIF($A$13:$A$66,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A9,$O$13:$O$65,"OK")</f>
+        <f>COUNTIFS($A$13:$A$66,$A9,$O$13:$O$66,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A9,$O$13:$O$65,"NG")</f>
+        <f>COUNTIFS($A$13:$A$66,$A9,$O$13:$O$66,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$65,$A10)</f>
+        <f>COUNTIF($A$13:$A$66,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A10,$O$13:$O$65,"OK")</f>
+        <f>COUNTIFS($A$13:$A$66,$A10,$O$13:$O$66,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$65,$A10,$O$13:$O$65,"NG")</f>
+        <f>COUNTIFS($A$13:$A$66,$A10,$O$13:$O$66,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$65,"L0*",$O$13:$O$65,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$65,"L1*",$O$13:$O$65,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$65,"L0*",$O$13:$O$65,"OK")+COUNTIFS($E$13:$E$65,"L1*",$O$13:$O$65,"OK")&lt;COUNTIF($E$13:$E$65,"L0*")+COUNTIF($E$13:$E$65,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$66,"L0*",$O$13:$O$66,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$66,"L1*",$O$13:$O$66,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$66,"L0*",$O$13:$O$66,"OK")+COUNTIFS($E$13:$E$66,"L1*",$O$13:$O$66,"OK")&lt;COUNTIF($E$13:$E$66,"L0*")+COUNTIF($E$13:$E$66,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -3320,18 +3320,18 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>T-D09 R-04</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する ／ 操作手順 ＞ 人件費の計算方法</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M46" s="9" t="inlineStr"/>
       <c r="N46" s="9" t="inlineStr">
         <is>
-          <t>T-D09.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="O46" s="12" t="inlineStr"/>
@@ -3339,7 +3339,7 @@
       <c r="Q46" s="12" t="inlineStr"/>
       <c r="R46" s="12" t="inlineStr"/>
     </row>
-    <row r="47" ht="64" customHeight="1">
+    <row r="47" ht="49" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -3387,23 +3387,23 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>人件費実績／設定履歴／従業員詳細</t>
+          <t>人件費実績／設定履歴／給与実績一覧</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>T-D09 T-H04 T-A07</t>
+          <t>T-P01 T-H04 T-A07</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する ／ ケース別 ＞ 数字が合わないとき ／ 操作手順 ＞ データを出力する</t>
+          <t>操作手順 ＞ データを出力する ／ ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M47" s="9" t="inlineStr"/>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>T-D09.png</t>
+          <t>T-P01.png</t>
         </is>
       </c>
       <c r="O47" s="12" t="inlineStr"/>
@@ -4695,14 +4695,86 @@
       <c r="Q65" s="12" t="inlineStr"/>
       <c r="R65" s="12" t="inlineStr"/>
     </row>
+    <row r="66" ht="79" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>M4 顧客とCSが自分で運用できる</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>画面：通して見る場所がある</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>AC-54</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>1名分の実績を期間で通して確認でき、その内容をCSVで出力できる</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>年月の範囲指定で年をまたいで表示できる（またげない=0件）。月次・日次の両タブで表示中の内容がそのままCSVに出る（画面の行数との差=0件）。給与計算モードの切替が月次で効く</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>従業員詳細から従業員コードを引き継いで開く。年月は開始・終了の2つで指定する。日次タブでは給与計算モードを出さない（日別に概算は無いため）</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>給与実績一覧</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>T-D09 T-P01</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する ／ 操作手順 ＞ データを出力する</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr"/>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t>T-D09.png</t>
+        </is>
+      </c>
+      <c r="O66" s="12" t="inlineStr"/>
+      <c r="P66" s="13" t="inlineStr"/>
+      <c r="Q66" s="12" t="inlineStr"/>
+      <c r="R66" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R65"/>
+  <autoFilter ref="A12:R66"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O65">
+  <conditionalFormatting sqref="O13:O66">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4719,7 +4791,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -1831,7 +1831,7 @@
       <c r="Q25" s="12" t="inlineStr"/>
       <c r="R25" s="12" t="inlineStr"/>
     </row>
-    <row r="26" ht="49" customHeight="1">
+    <row r="26" ht="64" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>按分額が実績給与×ヘルプ時間÷総労働時間と一致</t>
+          <t>按分額が （概算給与＋深夜残業代＋みなし超過残業代）×ヘルプ時間÷総労働時間 と一致し、そこにヘルプ先の交通費を加えた額がヘルプ人件費になる（差分0円）</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>日別の勤務店舗を保持し、店舗別集計時に振り替える</t>
+          <t>按分の基礎は交通費を除いた給与部分。交通費は実費なので時間按分しない。ヘルプ先の交通費だけを按分額に足して1つの列に出す</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
@@ -1903,7 +1903,7 @@
       <c r="Q26" s="12" t="inlineStr"/>
       <c r="R26" s="12" t="inlineStr"/>
     </row>
-    <row r="27" ht="49" customHeight="1">
+    <row r="27" ht="79" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>原則③：交通費の帰属</t>
+          <t>原則③：交通費も働いた店舗に付ける</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>交通費が独立費目として一意に計上される</t>
+          <t>交通費が人件費に含まれ、働いた店舗に計上される</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>実績給与に交通費を含まない／通勤は所属店舗・ヘルプ先は応援先に計上（店舗別合計100,000円）</t>
+          <t>実績給与＝概算給与＋深夜残業代＋みなし超過残業代＋所属店舗の交通費＋ヘルプ先の交通費（差分0円）。ヘルプ先の交通費は応援先に計上され、店舗別合計＝全社（差0円）</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>判断6＝独立列。給与とは別カラムで持ち、総支給額＝給与＋交通費で表示</t>
+          <t>一覧とエクスポートに交通費の列を出さない。設定側（単位交通費・ヘルプ先交通費）は入力項目として保持し、実績の計算時に人件費へ合算する</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別・日別）</t>
+          <t>人件費実績（月別・日別）／給与実績一覧</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$66,$A5)</f>
+        <f>COUNTIF($A$13:$A$68,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A5,$O$13:$O$66,"OK")</f>
+        <f>COUNTIFS($A$13:$A$68,$A5,$O$13:$O$68,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A5,$O$13:$O$66,"NG")</f>
+        <f>COUNTIFS($A$13:$A$68,$A5,$O$13:$O$68,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$66,$A6)</f>
+        <f>COUNTIF($A$13:$A$68,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A6,$O$13:$O$66,"OK")</f>
+        <f>COUNTIFS($A$13:$A$68,$A6,$O$13:$O$68,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A6,$O$13:$O$66,"NG")</f>
+        <f>COUNTIFS($A$13:$A$68,$A6,$O$13:$O$68,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$66,$A7)</f>
+        <f>COUNTIF($A$13:$A$68,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A7,$O$13:$O$66,"OK")</f>
+        <f>COUNTIFS($A$13:$A$68,$A7,$O$13:$O$68,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A7,$O$13:$O$66,"NG")</f>
+        <f>COUNTIFS($A$13:$A$68,$A7,$O$13:$O$68,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$66,$A8)</f>
+        <f>COUNTIF($A$13:$A$68,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A8,$O$13:$O$66,"OK")</f>
+        <f>COUNTIFS($A$13:$A$68,$A8,$O$13:$O$68,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A8,$O$13:$O$66,"NG")</f>
+        <f>COUNTIFS($A$13:$A$68,$A8,$O$13:$O$68,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$66,$A9)</f>
+        <f>COUNTIF($A$13:$A$68,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A9,$O$13:$O$66,"OK")</f>
+        <f>COUNTIFS($A$13:$A$68,$A9,$O$13:$O$68,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A9,$O$13:$O$66,"NG")</f>
+        <f>COUNTIFS($A$13:$A$68,$A9,$O$13:$O$68,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$66,$A10)</f>
+        <f>COUNTIF($A$13:$A$68,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A10,$O$13:$O$66,"OK")</f>
+        <f>COUNTIFS($A$13:$A$68,$A10,$O$13:$O$68,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$66,$A10,$O$13:$O$66,"NG")</f>
+        <f>COUNTIFS($A$13:$A$68,$A10,$O$13:$O$68,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$66,"L0*",$O$13:$O$66,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$66,"L1*",$O$13:$O$66,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$66,"L0*",$O$13:$O$66,"OK")+COUNTIFS($E$13:$E$66,"L1*",$O$13:$O$66,"OK")&lt;COUNTIF($E$13:$E$66,"L0*")+COUNTIF($E$13:$E$66,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$68,"L0*",$O$13:$O$68,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$68,"L1*",$O$13:$O$68,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$68,"L0*",$O$13:$O$68,"OK")+COUNTIFS($E$13:$E$68,"L1*",$O$13:$O$68,"OK")&lt;COUNTIF($E$13:$E$68,"L0*")+COUNTIF($E$13:$E$68,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="12" t="inlineStr"/>
     </row>
-    <row r="19" ht="49" customHeight="1">
+    <row r="19" ht="64" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>同じ従業員コードが二重に登録されない</t>
+          <t>同じ外部IDが二重に登録されず、同じ従業員に紐づく</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>二重登録=0件（2回目は更新・件数増加なし）</t>
+          <t>二重登録=0件（同じ外部IDの2回目は更新となり件数が増えない）。1つの外部IDが2つの従業員IDに紐づく=0件</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>従業員コードに一意制約。取込はコードをキーにupsert。CSV内の重複行は事前に検出</t>
+          <t>突合キーは「勤怠システム＋外部ID」。この組で従業員IDを引き、無ければ取込を止める。従業員コードでは突合しない</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>設定インポート／従業員一覧</t>
+          <t>設定インポート／実績取込データ</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
@@ -4767,14 +4767,158 @@
       <c r="Q66" s="12" t="inlineStr"/>
       <c r="R66" s="12" t="inlineStr"/>
     </row>
+    <row r="67" ht="79" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>M1 過去が動かない構造ができる</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>設定が適用日付つきで保存され、履歴が積まれる。同じ従業員コードが二重に登録されない</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>データ保全：従業員の同一性を保つ</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>AC-55</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>L0 リリース不可</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>従業員にラクミー側の従業員IDが付番され、履歴と実績がそれに紐づく</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>従業員IDが無い従業員=0件。外部IDを変更しても、その従業員の設定変更履歴と過去月の実績が変わらない（差分0円・0件）</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>★中止</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>従業員IDは登録時に自動付番し、あとから変更しない。履歴・実績の外部キーは従業員IDにする。従業員コードと外部IDは表示・突合のための属性として持つ</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>従業員一覧／従業員詳細</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>T-I20 T-Z02 R-01</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき ／ ケース別 ＞ すでにご利用中のお客様 ／ ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr"/>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t>T-I20.png</t>
+        </is>
+      </c>
+      <c r="O67" s="12" t="inlineStr"/>
+      <c r="P67" s="13" t="inlineStr"/>
+      <c r="Q67" s="12" t="inlineStr"/>
+      <c r="R67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68" ht="64" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>M4 顧客とCSが自分で運用できる</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>入出力：ID体系の違いを吸収</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>AC-56</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>勤怠システムごとの外部IDを従業員IDに対応づけられる</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>1名が複数の勤怠システムの外部IDを持てる（E0001＝King of Time 1001／ジョブカン JB-001）。対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>「勤怠システム＋外部ID → 従業員ID」の対応をデータで保持する。列名の対応（列マッピングテンプレート）とは別に持つ</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート／設定インポート</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>T-I17 T-I20</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります ／ ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>T-I17.png</t>
+        </is>
+      </c>
+      <c r="O68" s="12" t="inlineStr"/>
+      <c r="P68" s="13" t="inlineStr"/>
+      <c r="Q68" s="12" t="inlineStr"/>
+      <c r="R68" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R66"/>
+  <autoFilter ref="A12:R68"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O66">
+  <conditionalFormatting sqref="O13:O68">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4791,7 +4935,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$68,$A5)</f>
+        <f>COUNTIF($A$13:$A$69,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A5,$O$13:$O$68,"OK")</f>
+        <f>COUNTIFS($A$13:$A$69,$A5,$O$13:$O$69,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A5,$O$13:$O$68,"NG")</f>
+        <f>COUNTIFS($A$13:$A$69,$A5,$O$13:$O$69,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$68,$A6)</f>
+        <f>COUNTIF($A$13:$A$69,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A6,$O$13:$O$68,"OK")</f>
+        <f>COUNTIFS($A$13:$A$69,$A6,$O$13:$O$69,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A6,$O$13:$O$68,"NG")</f>
+        <f>COUNTIFS($A$13:$A$69,$A6,$O$13:$O$69,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$68,$A7)</f>
+        <f>COUNTIF($A$13:$A$69,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A7,$O$13:$O$68,"OK")</f>
+        <f>COUNTIFS($A$13:$A$69,$A7,$O$13:$O$69,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A7,$O$13:$O$68,"NG")</f>
+        <f>COUNTIFS($A$13:$A$69,$A7,$O$13:$O$69,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$68,$A8)</f>
+        <f>COUNTIF($A$13:$A$69,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A8,$O$13:$O$68,"OK")</f>
+        <f>COUNTIFS($A$13:$A$69,$A8,$O$13:$O$69,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A8,$O$13:$O$68,"NG")</f>
+        <f>COUNTIFS($A$13:$A$69,$A8,$O$13:$O$69,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$68,$A9)</f>
+        <f>COUNTIF($A$13:$A$69,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A9,$O$13:$O$68,"OK")</f>
+        <f>COUNTIFS($A$13:$A$69,$A9,$O$13:$O$69,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A9,$O$13:$O$68,"NG")</f>
+        <f>COUNTIFS($A$13:$A$69,$A9,$O$13:$O$69,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$68,$A10)</f>
+        <f>COUNTIF($A$13:$A$69,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A10,$O$13:$O$68,"OK")</f>
+        <f>COUNTIFS($A$13:$A$69,$A10,$O$13:$O$69,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$68,$A10,$O$13:$O$68,"NG")</f>
+        <f>COUNTIFS($A$13:$A$69,$A10,$O$13:$O$69,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$68,"L0*",$O$13:$O$68,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$68,"L1*",$O$13:$O$68,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$68,"L0*",$O$13:$O$68,"OK")+COUNTIFS($E$13:$E$68,"L1*",$O$13:$O$68,"OK")&lt;COUNTIF($E$13:$E$68,"L0*")+COUNTIF($E$13:$E$68,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$69,"L0*",$O$13:$O$69,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$69,"L1*",$O$13:$O$69,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$69,"L0*",$O$13:$O$69,"OK")+COUNTIFS($E$13:$E$69,"L1*",$O$13:$O$69,"OK")&lt;COUNTIF($E$13:$E$69,"L0*")+COUNTIF($E$13:$E$69,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -4911,14 +4911,86 @@
       <c r="Q68" s="12" t="inlineStr"/>
       <c r="R68" s="12" t="inlineStr"/>
     </row>
+    <row r="69" ht="79" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>M4 顧客とCSが自分で運用できる</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>画面：実績が出る前も金額が見える</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>AC-57</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>概算と実績を切り替えられ、差分が読める</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>3画面すべてで概算⇄実績を切り替えられる。実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>概算モードは基本列のみ、実績モードで実績列を追加表示する。従業員詳細では絞り込みではなく表示の切替として持つ（月次／日次タブと同じ扱い）</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>人件費実績（月別）／給与実績一覧／従業員詳細（給与実績）</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>T-D09 T-P02 T-A02</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr"/>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>T-D09.png</t>
+        </is>
+      </c>
+      <c r="O69" s="12" t="inlineStr"/>
+      <c r="P69" s="13" t="inlineStr"/>
+      <c r="Q69" s="12" t="inlineStr"/>
+      <c r="R69" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R68"/>
+  <autoFilter ref="A12:R69"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O68">
+  <conditionalFormatting sqref="O13:O69">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4935,7 +5007,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$69,$A5)</f>
+        <f>COUNTIF($A$13:$A$70,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A5,$O$13:$O$69,"OK")</f>
+        <f>COUNTIFS($A$13:$A$70,$A5,$O$13:$O$70,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A5,$O$13:$O$69,"NG")</f>
+        <f>COUNTIFS($A$13:$A$70,$A5,$O$13:$O$70,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$69,$A6)</f>
+        <f>COUNTIF($A$13:$A$70,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A6,$O$13:$O$69,"OK")</f>
+        <f>COUNTIFS($A$13:$A$70,$A6,$O$13:$O$70,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A6,$O$13:$O$69,"NG")</f>
+        <f>COUNTIFS($A$13:$A$70,$A6,$O$13:$O$70,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$69,$A7)</f>
+        <f>COUNTIF($A$13:$A$70,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A7,$O$13:$O$69,"OK")</f>
+        <f>COUNTIFS($A$13:$A$70,$A7,$O$13:$O$70,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A7,$O$13:$O$69,"NG")</f>
+        <f>COUNTIFS($A$13:$A$70,$A7,$O$13:$O$70,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$69,$A8)</f>
+        <f>COUNTIF($A$13:$A$70,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A8,$O$13:$O$69,"OK")</f>
+        <f>COUNTIFS($A$13:$A$70,$A8,$O$13:$O$70,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A8,$O$13:$O$69,"NG")</f>
+        <f>COUNTIFS($A$13:$A$70,$A8,$O$13:$O$70,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$69,$A9)</f>
+        <f>COUNTIF($A$13:$A$70,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A9,$O$13:$O$69,"OK")</f>
+        <f>COUNTIFS($A$13:$A$70,$A9,$O$13:$O$70,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A9,$O$13:$O$69,"NG")</f>
+        <f>COUNTIFS($A$13:$A$70,$A9,$O$13:$O$70,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$69,$A10)</f>
+        <f>COUNTIF($A$13:$A$70,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A10,$O$13:$O$69,"OK")</f>
+        <f>COUNTIFS($A$13:$A$70,$A10,$O$13:$O$70,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$69,$A10,$O$13:$O$69,"NG")</f>
+        <f>COUNTIFS($A$13:$A$70,$A10,$O$13:$O$70,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$69,"L0*",$O$13:$O$69,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$69,"L1*",$O$13:$O$69,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$69,"L0*",$O$13:$O$69,"OK")+COUNTIFS($E$13:$E$69,"L1*",$O$13:$O$69,"OK")&lt;COUNTIF($E$13:$E$69,"L0*")+COUNTIF($E$13:$E$69,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$70,"L0*",$O$13:$O$70,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$70,"L1*",$O$13:$O$70,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$70,"L0*",$O$13:$O$70,"OK")+COUNTIFS($E$13:$E$70,"L1*",$O$13:$O$70,"OK")&lt;COUNTIF($E$13:$E$70,"L0*")+COUNTIF($E$13:$E$70,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -4911,7 +4911,7 @@
       <c r="Q68" s="12" t="inlineStr"/>
       <c r="R68" s="12" t="inlineStr"/>
     </row>
-    <row r="69" ht="79" customHeight="1">
+    <row r="69" ht="94" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>3画面すべてで概算⇄実績を切り替えられる。実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）</t>
+          <t>3画面すべてで概算⇄実績を切り替えられる。実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -4959,17 +4959,17 @@
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）／給与実績一覧／従業員詳細（給与実績）</t>
+          <t>人件費実績（月別）／給与実績一覧／従業員詳細（給与実績）／設定・実績エクスポート</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>T-D09 T-P02 T-A02</t>
+          <t>T-D09 T-P02 T-A02 T-E09</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する ／ 操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M69" s="9" t="inlineStr"/>
@@ -4983,14 +4983,86 @@
       <c r="Q69" s="12" t="inlineStr"/>
       <c r="R69" s="12" t="inlineStr"/>
     </row>
+    <row r="70" ht="64" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>M4 顧客とCSが自分で運用できる</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>AC-58</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>L2 次段階</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>従業員一覧から、絞り込んだ店舗のまま人件費実績と設定変更履歴へ移動できる</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>店舗で絞った状態から2経路とも到達し、遷移先が同じ店舗で絞り込まれている（絞り込みが引き継がれない=0件）</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>影響なし</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>従業員一覧の店舗フィルタの値を引き継いで遷移する。画面は新設せず既存の人件費実績・従業員設定履歴を開く</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>T-L06</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr"/>
+      <c r="N70" s="9" t="inlineStr">
+        <is>
+          <t>T-L06.png</t>
+        </is>
+      </c>
+      <c r="O70" s="12" t="inlineStr"/>
+      <c r="P70" s="13" t="inlineStr"/>
+      <c r="Q70" s="12" t="inlineStr"/>
+      <c r="R70" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R69"/>
+  <autoFilter ref="A12:R70"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O69">
+  <conditionalFormatting sqref="O13:O70">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5007,7 +5079,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別・実績）</t>
+          <t>給与実績一覧（月別・実績）</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別・実績）</t>
+          <t>給与実績一覧（月別・実績）</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別・概算）</t>
+          <t>給与実績一覧（月別・概算）</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別・概算）</t>
+          <t>給与実績一覧（月別・概算）</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（日別）／月別</t>
+          <t>給与実績一覧（日別）／月別</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別・日別）／給与実績一覧</t>
+          <t>給与実績一覧（月別・日別）／従業員別 給与実績</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>仕様書 第2部の遷移どおりに画面が繋がる（取込データ⇄人件費実績の相互導線を含む）</t>
+          <t>仕様書 第2部の遷移どおりに画面が繋がる（取込データ⇄給与実績一覧の相互導線を含む）</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>人件費実績／設定履歴／給与実績一覧</t>
+          <t>給与実績一覧／設定履歴／従業員別 給与実績</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>人件費実績／従業員詳細</t>
+          <t>給与実績一覧／従業員詳細</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K55" s="9" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K57" s="9" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）</t>
+          <t>給与実績一覧（月別）</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>「実績データ取込」で勤怠実績が取り込まれ、人件費実績に反映されること</t>
+          <t>「実績データ取込」で勤怠実績が取り込まれ、給与実績一覧に反映されること</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>従業員詳細と人件費実績のモーダル、どちらから編集しても適用日付と履歴が同じ形式で残ること</t>
+          <t>従業員詳細と給与実績一覧のモーダル、どちらから編集しても適用日付と履歴が同じ形式で残ること</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（設定編集モーダル）／従業員詳細</t>
+          <t>給与実績一覧（設定編集モーダル）／従業員詳細</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>条件付きGo可（取込後に人件費実績で確認する運用で代替。ただし気づくのが遅れる）</t>
+          <t>条件付きGo可（取込後に給与実績一覧で確認する運用で代替。ただし気づくのが遅れる）</t>
         </is>
       </c>
       <c r="I62" s="9" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>変わった項目の強調＝変更箇所と一致（過不足0件）。「すべての履歴」から従業員設定履歴へ遷移し、その従業員で絞り込まれた状態で開く（絞り込みなしでの遷移=0件）</t>
+          <t>変わった項目の強調＝変更箇所と一致（過不足0件）。「すべての履歴」から設定変更履歴一覧へ遷移し、その従業員で絞り込まれた状態で開く（絞り込みなしでの遷移=0件）</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>直前行との差分を項目単位で判定して強調する。「すべての履歴」は従業員コードを引き継いで従業員設定履歴を開く</t>
+          <t>直前行との差分を項目単位で判定して強調する。「すべての履歴」は従業員コードを引き継いで設定変更履歴一覧を開く</t>
         </is>
       </c>
       <c r="J65" s="9" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>給与実績一覧</t>
+          <t>従業員別 給与実績</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>人件費実績（月別）／給与実績一覧／従業員詳細（給与実績）／設定・実績エクスポート</t>
+          <t>給与実績一覧（月別）／従業員別 給与実績／従業員詳細（給与実績）／設定・実績エクスポート</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>従業員一覧から、絞り込んだ店舗のまま人件費実績と設定変更履歴へ移動できる</t>
+          <t>従業員一覧から、絞り込んだ店舗のまま給与実績一覧と設定変更履歴へ移動できる</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>従業員一覧の店舗フィルタの値を引き継いで遷移する。画面は新設せず既存の人件費実績・従業員設定履歴を開く</t>
+          <t>従業員一覧の店舗フィルタの値を引き継いで遷移する。画面は新設せず既存の給与実績一覧・設定変更履歴一覧を開く</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4911,7 +4911,7 @@
       <c r="Q68" s="12" t="inlineStr"/>
       <c r="R68" s="12" t="inlineStr"/>
     </row>
-    <row r="69" ht="94" customHeight="1">
+    <row r="69" ht="139" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>3画面すべてで概算⇄実績を切り替えられる。実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる</t>
+          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別はモード切替を持たないが、想定給与・給与実績差分が表示される（欠落=0件）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>概算モードは基本列のみ、実績モードで実績列を追加表示する。従業員詳細では絞り込みではなく表示の切替として持つ（月次／日次タブと同じ扱い）</t>
+          <t>月別は概算モードで基本列のみ、実績モードで実績列を追加表示する。日別はモード切替を置かず常に実績表示とし、その中に想定給与・給与実績差分を含める。日次の想定給与は月額の単価を所定労働日割（判断1）で1日あたりに割った額。従業員詳細では絞り込みではなく表示の切替として持つ</t>
         </is>
       </c>
       <c r="J69" s="9" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>T-D09 T-P02 T-A02 T-E09</t>
+          <t>T-D09 T-P02 T-A02 T-A05 T-E09</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$70,$A5)</f>
+        <f>COUNTIF($A$13:$A$71,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A5,$O$13:$O$70,"OK")</f>
+        <f>COUNTIFS($A$13:$A$71,$A5,$O$13:$O$71,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A5,$O$13:$O$70,"NG")</f>
+        <f>COUNTIFS($A$13:$A$71,$A5,$O$13:$O$71,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$70,$A6)</f>
+        <f>COUNTIF($A$13:$A$71,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A6,$O$13:$O$70,"OK")</f>
+        <f>COUNTIFS($A$13:$A$71,$A6,$O$13:$O$71,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A6,$O$13:$O$70,"NG")</f>
+        <f>COUNTIFS($A$13:$A$71,$A6,$O$13:$O$71,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$70,$A7)</f>
+        <f>COUNTIF($A$13:$A$71,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A7,$O$13:$O$70,"OK")</f>
+        <f>COUNTIFS($A$13:$A$71,$A7,$O$13:$O$71,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A7,$O$13:$O$70,"NG")</f>
+        <f>COUNTIFS($A$13:$A$71,$A7,$O$13:$O$71,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$70,$A8)</f>
+        <f>COUNTIF($A$13:$A$71,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A8,$O$13:$O$70,"OK")</f>
+        <f>COUNTIFS($A$13:$A$71,$A8,$O$13:$O$71,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A8,$O$13:$O$70,"NG")</f>
+        <f>COUNTIFS($A$13:$A$71,$A8,$O$13:$O$71,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$70,$A9)</f>
+        <f>COUNTIF($A$13:$A$71,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A9,$O$13:$O$70,"OK")</f>
+        <f>COUNTIFS($A$13:$A$71,$A9,$O$13:$O$71,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A9,$O$13:$O$70,"NG")</f>
+        <f>COUNTIFS($A$13:$A$71,$A9,$O$13:$O$71,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$70,$A10)</f>
+        <f>COUNTIF($A$13:$A$71,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A10,$O$13:$O$70,"OK")</f>
+        <f>COUNTIFS($A$13:$A$71,$A10,$O$13:$O$71,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$70,$A10,$O$13:$O$70,"NG")</f>
+        <f>COUNTIFS($A$13:$A$71,$A10,$O$13:$O$71,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$70,"L0*",$O$13:$O$70,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$70,"L1*",$O$13:$O$70,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$70,"L0*",$O$13:$O$70,"OK")+COUNTIFS($E$13:$E$70,"L1*",$O$13:$O$70,"OK")&lt;COUNTIF($E$13:$E$70,"L0*")+COUNTIF($E$13:$E$70,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$71,"L0*",$O$13:$O$71,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$71,"L1*",$O$13:$O$71,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$71,"L0*",$O$13:$O$71,"OK")+COUNTIFS($E$13:$E$71,"L1*",$O$13:$O$71,"OK")&lt;COUNTIF($E$13:$E$71,"L0*")+COUNTIF($E$13:$E$71,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -5055,14 +5055,86 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
+    <row r="71" ht="94" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>M2 金額が算式どおりに出る</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>計算：日割りの分母を持つ</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>AC-59</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>想定労働日数が解決され、月給者の日割りが計算できる</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>従業員設定の想定労働日数が未入力なら月次予算設定の営業日数が使われる（解決できない従業員=0件）。入力があればそちらが優先される。日次の想定給与＝単位給与額÷想定労働日数（月給者）／単位給与額×実働時間（時給者）で、計算違い0件</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>想定労働日数は非必須。未入力時は月次予算設定の営業日数を参照する。営業日数が未設定の場合の扱いを決めておく（この機能単独では完結しない）</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>従業員登録／従業員詳細／給与実績一覧</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>C-018</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr"/>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>C-018.png</t>
+        </is>
+      </c>
+      <c r="O71" s="12" t="inlineStr"/>
+      <c r="P71" s="13" t="inlineStr"/>
+      <c r="Q71" s="12" t="inlineStr"/>
+      <c r="R71" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R70"/>
+  <autoFilter ref="A12:R71"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O70">
+  <conditionalFormatting sqref="O13:O71">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5079,7 +5151,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$71,$A5)</f>
+        <f>COUNTIF($A$13:$A$72,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A5,$O$13:$O$71,"OK")</f>
+        <f>COUNTIFS($A$13:$A$72,$A5,$O$13:$O$72,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A5,$O$13:$O$71,"NG")</f>
+        <f>COUNTIFS($A$13:$A$72,$A5,$O$13:$O$72,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$71,$A6)</f>
+        <f>COUNTIF($A$13:$A$72,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A6,$O$13:$O$71,"OK")</f>
+        <f>COUNTIFS($A$13:$A$72,$A6,$O$13:$O$72,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A6,$O$13:$O$71,"NG")</f>
+        <f>COUNTIFS($A$13:$A$72,$A6,$O$13:$O$72,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$71,$A7)</f>
+        <f>COUNTIF($A$13:$A$72,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A7,$O$13:$O$71,"OK")</f>
+        <f>COUNTIFS($A$13:$A$72,$A7,$O$13:$O$72,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A7,$O$13:$O$71,"NG")</f>
+        <f>COUNTIFS($A$13:$A$72,$A7,$O$13:$O$72,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$71,$A8)</f>
+        <f>COUNTIF($A$13:$A$72,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A8,$O$13:$O$71,"OK")</f>
+        <f>COUNTIFS($A$13:$A$72,$A8,$O$13:$O$72,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A8,$O$13:$O$71,"NG")</f>
+        <f>COUNTIFS($A$13:$A$72,$A8,$O$13:$O$72,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$71,$A9)</f>
+        <f>COUNTIF($A$13:$A$72,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A9,$O$13:$O$71,"OK")</f>
+        <f>COUNTIFS($A$13:$A$72,$A9,$O$13:$O$72,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A9,$O$13:$O$71,"NG")</f>
+        <f>COUNTIFS($A$13:$A$72,$A9,$O$13:$O$72,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$71,$A10)</f>
+        <f>COUNTIF($A$13:$A$72,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A10,$O$13:$O$71,"OK")</f>
+        <f>COUNTIFS($A$13:$A$72,$A10,$O$13:$O$72,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$71,$A10,$O$13:$O$71,"NG")</f>
+        <f>COUNTIFS($A$13:$A$72,$A10,$O$13:$O$72,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$71,"L0*",$O$13:$O$71,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$71,"L1*",$O$13:$O$71,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$71,"L0*",$O$13:$O$71,"OK")+COUNTIFS($E$13:$E$71,"L1*",$O$13:$O$71,"OK")&lt;COUNTIF($E$13:$E$71,"L0*")+COUNTIF($E$13:$E$71,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$72,"L0*",$O$13:$O$72,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$72,"L1*",$O$13:$O$72,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$72,"L0*",$O$13:$O$72,"OK")+COUNTIFS($E$13:$E$72,"L1*",$O$13:$O$72,"OK")&lt;COUNTIF($E$13:$E$72,"L0*")+COUNTIF($E$13:$E$72,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -5127,14 +5127,86 @@
       <c r="Q71" s="12" t="inlineStr"/>
       <c r="R71" s="12" t="inlineStr"/>
     </row>
+    <row r="72" ht="94" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>M2 金額が算式どおりに出る</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>計算：概算の日別は営業日でならす</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>AC-60</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>日別タブで概算モードに切り替えると、実績が無くても当月の見込みが日別に出る</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>日別タブに概算／実績の切替がある。概算モードの1日あたり＝月次の概算給与÷当月の営業日数（営業日は所属店舗の休業日設定から求める）。当月の全営業日に行が出て、日別の合計が月次の概算給与と1円の差もなく一致する（端数は最大剰余）</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>切替はモック実装済み。金額の配分はサーバ実装が必要。実績モードの想定給与列（月次概算÷想定労働日数）とは別の数字になるため、画面に注記があること</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>給与実績一覧 日別実績</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>C-019</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="inlineStr"/>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t>C-019.png</t>
+        </is>
+      </c>
+      <c r="O72" s="12" t="inlineStr"/>
+      <c r="P72" s="13" t="inlineStr"/>
+      <c r="Q72" s="12" t="inlineStr"/>
+      <c r="R72" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R71"/>
+  <autoFilter ref="A12:R72"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O71">
+  <conditionalFormatting sqref="O13:O72">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5151,7 +5223,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="94" customHeight="1">
+    <row r="71" ht="109" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>従業員設定の想定労働日数が未入力なら月次予算設定の営業日数が使われる（解決できない従業員=0件）。入力があればそちらが優先される。日次の想定給与＝単位給与額÷想定労働日数（月給者）／単位給与額×実働時間（時給者）で、計算違い0件</t>
+          <t>想定労働日数は月給者だけの項目。月給者は未入力なら所属店舗の休業日設定から求めた営業日数が使われる（解決できない月給者=0件）。入力があればそちらが優先される。日次の想定給与＝単位給与額÷想定労働日数（月給者）／単位給与額×実働時間（時給者。日数を使わないため入力欄を出さない）で、計算違い0件</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は非必須。未入力時は月次予算設定の営業日数を参照する。営業日数が未設定の場合の扱いを決めておく（この機能単独では完結しない）</t>
+          <t>想定労働日数は非必須。給与単位が時給の従業員には入力欄を出さない。未入力時は所属店舗の休業日設定から求めた営業日数を参照する。休業日設定が未設定の場合の扱いを決めておく（この機能単独では完結しない）</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別はモード切替を持たないが、想定給与・給与実績差分が表示される（欠落=0件）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる</t>
+          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別も概算⇄実績を切り替えられ、実績モードで想定給与・給与実績差分が表示される（欠落=0件。概算の日別はAC-60）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>月別は概算モードで基本列のみ、実績モードで実績列を追加表示する。日別はモード切替を置かず常に実績表示とし、その中に想定給与・給与実績差分を含める。日次の想定給与は月額の単価を所定労働日割（判断1）で1日あたりに割った額。従業員詳細では絞り込みではなく表示の切替として持つ</t>
+          <t>月別は概算モードで基本列のみ、実績モードで実績列を追加表示する。日別も概算⇄実績を切り替える（判断21）。実績モードに想定給与・給与実績差分を含める。日次の想定給与は月額の単価を所定労働日割（判断1）で1日あたりに割った額。従業員詳細では絞り込みではなく表示の切替として持つ</t>
         </is>
       </c>
       <c r="J69" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4911,7 +4911,7 @@
       <c r="Q68" s="12" t="inlineStr"/>
       <c r="R68" s="12" t="inlineStr"/>
     </row>
-    <row r="69" ht="139" customHeight="1">
+    <row r="69" ht="274" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別も概算⇄実績を切り替えられ、実績モードで想定給与・給与実績差分が表示される（欠落=0件。概算の日別はAC-60）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる</t>
+          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別も概算⇄実績を切り替えられ、実績モードで想定給与・給与実績差分が表示される（欠落=0件。概算の日別はAC-60）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる。概算モードで表示するのは実績データが無くても値が決まる列だけ（名前・日時/年月・雇用区分・所属店舗・給与単位・単位給与額・想定労働日数・想定労働時間/想定勤務時間・みなし労働時間・想定給与）。給与・給与実績差分・勤務日数・総労働時間/勤務時間・各差分・所属店舗労働時間・ヘルプ先店舗・ヘルプ時間・ヘルプ人件費・深夜残業時間・深夜残業代は実績モードのみ（判断22。3画面6タブで同じ）（食い違う列=0件）</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4911,7 +4911,7 @@
       <c r="Q68" s="12" t="inlineStr"/>
       <c r="R68" s="12" t="inlineStr"/>
     </row>
-    <row r="69" ht="274" customHeight="1">
+    <row r="69" ht="304" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別も概算⇄実績を切り替えられ、実績モードで想定給与・給与実績差分が表示される（欠落=0件。概算の日別はAC-60）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる。概算モードで表示するのは実績データが無くても値が決まる列だけ（名前・日時/年月・雇用区分・所属店舗・給与単位・単位給与額・想定労働日数・想定労働時間/想定勤務時間・みなし労働時間・想定給与）。給与・給与実績差分・勤務日数・総労働時間/勤務時間・各差分・所属店舗労働時間・ヘルプ先店舗・ヘルプ時間・ヘルプ人件費・深夜残業時間・深夜残業代は実績モードのみ（判断22。3画面6タブで同じ）（食い違う列=0件）</t>
+          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別も概算⇄実績を切り替えられ、実績モードで想定給与・給与実績差分が表示される（欠落=0件。概算の日別はAC-60）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる。概算モードで表示するのは実績データが無くても値が決まる列だけ（名前・日時/年月・雇用区分・所属店舗・給与単位・単位給与額・想定労働日数・想定労働時間/想定勤務時間・みなし労働時間・想定給与）。給与・給与実績差分・勤務日数・総労働時間/勤務時間・各差分・所属店舗労働時間・ヘルプ先店舗・ヘルプ時間・ヘルプ人件費・深夜残業時間・深夜残業代は実績モードのみ（判断22。3画面6タブで同じ）（食い違う列=0件）。想定給与に所属店舗の交通費が含まれ、ヘルプ先の交通費は含まれない（判断23）</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="109" customHeight="1">
+    <row r="71" ht="124" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は月給者だけの項目。月給者は未入力なら所属店舗の休業日設定から求めた営業日数が使われる（解決できない月給者=0件）。入力があればそちらが優先される。日次の想定給与＝単位給与額÷想定労働日数（月給者）／単位給与額×実働時間（時給者。日数を使わないため入力欄を出さない）で、計算違い0件</t>
+          <t>想定労働日数は月給者・時給者とも使う。未入力なら所属店舗の休業日設定から求めた営業日数が使われる（解決できない従業員=0件）。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月次の想定給与÷想定労働日数（判断23）。計算違い0件</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は非必須。給与単位が時給の従業員には入力欄を出さない。未入力時は所属店舗の休業日設定から求めた営業日数を参照する。休業日設定が未設定の場合の扱いを決めておく（この機能単独では完結しない）</t>
+          <t>想定労働日数は非必須だが月給者・時給者とも使う（日次の想定給与と、日額交通費の月次換算）。未入力時は所属店舗の休業日設定から求めた営業日数を参照する。休業日設定が未設定の場合の扱いを決めておく</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="124" customHeight="1">
+    <row r="71" ht="154" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は月給者・時給者とも使う。未入力なら所属店舗の休業日設定から求めた営業日数が使われる（解決できない従業員=0件）。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月次の想定給与÷想定労働日数（判断23）。計算違い0件</t>
+          <t>想定労働日数は月給者・時給者とも使う。未入力のときの既定値は、月給者は所属店舗の営業日数（休業日設定）、時給者は 切り上げ（所定労働時間÷8時間）で営業日数が上限（判断24）。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月次の想定給与÷想定労働日数（判断23）。計算違い0件</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は非必須だが月給者・時給者とも使う（日次の想定給与と、日額交通費の月次換算）。未入力時は所属店舗の休業日設定から求めた営業日数を参照する。休業日設定が未設定の場合の扱いを決めておく</t>
+          <t>想定労働日数は非必須。既定値は画面に薄字で出し、保存はしない（所定労働時間を変えたとき古い値が残らないようにする）。月給者は営業日数、時給者は 切り上げ（所定労働時間÷8時間）。休業日設定が未設定の場合の扱いを決めておく</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="154" customHeight="1">
+    <row r="71" ht="169" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は月給者・時給者とも使う。未入力のときの既定値は、月給者は所属店舗の営業日数（休業日設定）、時給者は 切り上げ（所定労働時間÷8時間）で営業日数が上限（判断24）。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月次の想定給与÷想定労働日数（判断23）。計算違い0件</t>
+          <t>想定労働日数は月給者・時給者とも使う。未入力のときの既定値は、月給者は所属店舗の営業日数（休業日設定）、時給者は 切り上げ（所定労働時間÷8時間）で営業日数が上限（判断24）。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="169" customHeight="1">
+    <row r="71" ht="199" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は月給者・時給者とも使う。未入力のときの既定値は、月給者は所属店舗の営業日数（休業日設定）、時給者は 切り上げ（所定労働時間÷8時間）で営業日数が上限（判断24）。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件</t>
+          <t>想定労働日数は月給者・時給者とも使う。未入力のとき、月給者は所属店舗の営業日数（休業日設定）を使う。時給者に既定値は置かない。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件。1日の想定勤務時間＝所定労働時間÷想定労働日数。想定労働日数が未入力の時給者は月次の想定給与だけ出て日次は「—」になる（判断26）</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は非必須。既定値は画面に薄字で出し、保存はしない（所定労働時間を変えたとき古い値が残らないようにする）。月給者は営業日数、時給者は 切り上げ（所定労働時間÷8時間）。休業日設定が未設定の場合の扱いを決めておく</t>
+          <t>想定労働日数は非必須。月給者は未入力なら所属店舗の営業日数。時給者に既定値は置かず、未入力なら日次の想定給与を「—」にして理由を添える（月次は出す）。休業日設定が未設定の場合の扱いを決めておく</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="199" customHeight="1">
+    <row r="71" ht="214" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は月給者・時給者とも使う。未入力のとき、月給者は所属店舗の営業日数（休業日設定）を使う。時給者に既定値は置かない。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件。1日の想定勤務時間＝所定労働時間÷想定労働日数。想定労働日数が未入力の時給者は月次の想定給与だけ出て日次は「—」になる（判断26）</t>
+          <t>想定労働日数は月給者・時給者とも使う。未入力のとき、月給者は所属店舗の営業日数（休業日設定）を使う。時給者に既定値は置かない。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件。1日の想定勤務時間＝所定労働時間÷想定労働日数。想定労働日数が未入力の時給者は、日次の想定給与と給与実績差分が「—」になる。日次の給与は勤怠実績から出るので必ず表示される（判断26）</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は非必須。月給者は未入力なら所属店舗の営業日数。時給者に既定値は置かず、未入力なら日次の想定給与を「—」にして理由を添える（月次は出す）。休業日設定が未設定の場合の扱いを決めておく</t>
+          <t>想定労働日数は非必須。月給者は未入力なら所属店舗の営業日数。時給者に既定値は置かず、未入力なら日次の想定給与と給与実績差分を「—」にして理由を添える。日次の給与は勤怠実績から必ず出す。月次も出す。休業日設定が未設定の場合の扱いを決めておく</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4911,7 +4911,7 @@
       <c r="Q68" s="12" t="inlineStr"/>
       <c r="R68" s="12" t="inlineStr"/>
     </row>
-    <row r="69" ht="304" customHeight="1">
+    <row r="69" ht="319" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別も概算⇄実績を切り替えられ、実績モードで想定給与・給与実績差分が表示される（欠落=0件。概算の日別はAC-60）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる。概算モードで表示するのは実績データが無くても値が決まる列だけ（名前・日時/年月・雇用区分・所属店舗・給与単位・単位給与額・想定労働日数・想定労働時間/想定勤務時間・みなし労働時間・想定給与）。給与・給与実績差分・勤務日数・総労働時間/勤務時間・各差分・所属店舗労働時間・ヘルプ先店舗・ヘルプ時間・ヘルプ人件費・深夜残業時間・深夜残業代は実績モードのみ（判断22。3画面6タブで同じ）（食い違う列=0件）。想定給与に所属店舗の交通費が含まれ、ヘルプ先の交通費は含まれない（判断23）</t>
+          <t>月別は概算⇄実績を切り替えられ、実績モードで 想定給与・給与・給与実績差分 が表示される（差分＝給与−想定給与、計算違い0件）。日別も概算⇄実績を切り替えられ、実績モードで想定給与・給与実績差分が表示される（欠落=0件。概算の日別はAC-60）。実績データ取込の前でも概算モードで金額が表示される（空欄=0件）。エクスポートの実績項目に給与実績差分が選べる。概算モードで表示するのは実績データが無くても値が決まる列だけ（名前・日時/年月・雇用区分・所属店舗・給与単位・単位給与額・想定労働日数・想定労働時間/想定勤務時間・みなし労働時間・想定給与）。給与・給与実績差分・勤務日数・総労働時間/勤務時間・各差分・所属店舗労働時間・ヘルプ先店舗・ヘルプ時間・ヘルプ人件費・深夜残業時間・深夜残業代は実績モードのみ（判断22。3画面6タブで同じ）（食い違う列=0件）。想定給与に所属店舗の交通費が含まれ、ヘルプ先の交通費は含まれない（判断23）。時給者の日次には想定給与・給与実績差分を出さない（判断27）</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="214" customHeight="1">
+    <row r="71" ht="229" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は月給者・時給者とも使う。未入力のとき、月給者は所属店舗の営業日数（休業日設定）を使う。時給者に既定値は置かない。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件。1日の想定勤務時間＝所定労働時間÷想定労働日数。想定労働日数が未入力の時給者は、日次の想定給与と給与実績差分が「—」になる。日次の給与は勤怠実績から出るので必ず表示される（判断26）</t>
+          <t>想定労働日数は月給者・時給者とも使う。未入力のとき、月給者は所属店舗の営業日数（休業日設定）を使う。時給者に既定値は置かない。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件。想定労働日数は日額交通費の月次換算（単位交通費×想定労働日数）と、月給者の日次按分に使う。時給者の日次は想定勤務時間・想定給与・給与実績差分を出さず「—」にする。日次の給与（実績）は出す。月次は出す（判断27）</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は非必須。月給者は未入力なら所属店舗の営業日数。時給者に既定値は置かず、未入力なら日次の想定給与と給与実績差分を「—」にして理由を添える。日次の給与は勤怠実績から必ず出す。月次も出す。休業日設定が未設定の場合の扱いを決めておく</t>
+          <t>想定労働日数は非必須。用途は日額交通費の月次換算と、月給者の日次按分。月給者は未入力なら所属店舗の営業日数。時給者の日次は想定給与・給与実績差分を出さず「—」にする（給与は出す）</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>設定インポート／実績取込データ</t>
+          <t>設定インポート／実績の取込結果</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ</t>
+          <t>設定の取込結果／実績の取込結果</t>
         </is>
       </c>
       <c r="K49" s="9" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ</t>
+          <t>設定の取込結果／実績の取込結果</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5055,7 +5055,7 @@
       <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr"/>
     </row>
-    <row r="71" ht="229" customHeight="1">
+    <row r="71" ht="259" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は月給者・時給者とも使う。未入力のとき、月給者は所属店舗の営業日数（休業日設定）を使う。時給者に既定値は置かない。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件。想定労働日数は日額交通費の月次換算（単位交通費×想定労働日数）と、月給者の日次按分に使う。時給者の日次は想定勤務時間・想定給与・給与実績差分を出さず「—」にする。日次の給与（実績）は出す。月次は出す（判断27）</t>
+          <t>想定労働日数は月給者・時給者とも使う。想定労働日数の既定値は直近3か月の平均出勤日数（勤怠取込の打刻）。入力があればそちらが優先。打刻が無いときだけ月給者は所属店舗の営業日数を使う（判断28）。解決できない従業員=0件。想定給与＝基本給の想定＋所属店舗の交通費（交通費単位が日額なら 単位交通費×想定労働日数）。ヘルプ先の交通費は含めない。日次の想定給与＝月給者は月次の想定給与÷想定労働日数／時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費（判断25）。計算違い0件。想定労働日数は日額交通費の月次換算（単位交通費×想定労働日数）と、月給者の日次按分に使う。時給者の日次は想定勤務時間・想定給与・給与実績差分を出さず「—」にする。日次の給与（実績）は出す。月次は出す（判断27）</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>想定労働日数は非必須。用途は日額交通費の月次換算と、月給者の日次按分。月給者は未入力なら所属店舗の営業日数。時給者の日次は想定給与・給与実績差分を出さず「—」にする（給与は出す）</t>
+          <t>想定労働日数は非必須。既定値は勤怠取込の打刻から直近3か月の平均出勤日数を求める（社員・アルバイト共通）。打刻が無いときだけ月給者は所属店舗の営業日数。用途は日額交通費の月次換算と月給者の日次按分。時給者の日次は想定給与・給与実績差分を出さず「—」にする</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$72,$A5)</f>
+        <f>COUNTIF($A$13:$A$73,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A5,$O$13:$O$72,"OK")</f>
+        <f>COUNTIFS($A$13:$A$73,$A5,$O$13:$O$73,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A5,$O$13:$O$72,"NG")</f>
+        <f>COUNTIFS($A$13:$A$73,$A5,$O$13:$O$73,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$72,$A6)</f>
+        <f>COUNTIF($A$13:$A$73,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A6,$O$13:$O$72,"OK")</f>
+        <f>COUNTIFS($A$13:$A$73,$A6,$O$13:$O$73,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A6,$O$13:$O$72,"NG")</f>
+        <f>COUNTIFS($A$13:$A$73,$A6,$O$13:$O$73,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$72,$A7)</f>
+        <f>COUNTIF($A$13:$A$73,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A7,$O$13:$O$72,"OK")</f>
+        <f>COUNTIFS($A$13:$A$73,$A7,$O$13:$O$73,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A7,$O$13:$O$72,"NG")</f>
+        <f>COUNTIFS($A$13:$A$73,$A7,$O$13:$O$73,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$72,$A8)</f>
+        <f>COUNTIF($A$13:$A$73,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A8,$O$13:$O$72,"OK")</f>
+        <f>COUNTIFS($A$13:$A$73,$A8,$O$13:$O$73,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A8,$O$13:$O$72,"NG")</f>
+        <f>COUNTIFS($A$13:$A$73,$A8,$O$13:$O$73,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$72,$A9)</f>
+        <f>COUNTIF($A$13:$A$73,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A9,$O$13:$O$72,"OK")</f>
+        <f>COUNTIFS($A$13:$A$73,$A9,$O$13:$O$73,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A9,$O$13:$O$72,"NG")</f>
+        <f>COUNTIFS($A$13:$A$73,$A9,$O$13:$O$73,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$72,$A10)</f>
+        <f>COUNTIF($A$13:$A$73,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A10,$O$13:$O$72,"OK")</f>
+        <f>COUNTIFS($A$13:$A$73,$A10,$O$13:$O$73,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$72,$A10,$O$13:$O$72,"NG")</f>
+        <f>COUNTIFS($A$13:$A$73,$A10,$O$13:$O$73,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$72,"L0*",$O$13:$O$72,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$72,"L1*",$O$13:$O$72,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$72,"L0*",$O$13:$O$72,"OK")+COUNTIFS($E$13:$E$72,"L1*",$O$13:$O$72,"OK")&lt;COUNTIF($E$13:$E$72,"L0*")+COUNTIF($E$13:$E$72,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$73,"L0*",$O$13:$O$73,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$73,"L1*",$O$13:$O$73,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$73,"L0*",$O$13:$O$73,"OK")+COUNTIFS($E$13:$E$73,"L1*",$O$13:$O$73,"OK")&lt;COUNTIF($E$13:$E$73,"L0*")+COUNTIF($E$13:$E$73,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -5199,14 +5199,86 @@
       <c r="Q72" s="12" t="inlineStr"/>
       <c r="R72" s="12" t="inlineStr"/>
     </row>
+    <row r="73" ht="94" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>M4 顧客とCSが自分で運用できる</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>原則②：起きた記録は書き換えない</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>AC-61</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>適用済みの設定変更履歴は編集も削除もできない</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>予約中の行にだけ編集・削除ボタンが出る。適用中・過去の行は表示ボタンのみ（編集・削除ボタン=0件）。APIを直接呼んでも適用済みの履歴は更新・削除できない（成功=0件）。設定変更履歴一覧にも操作列があり同じ規則で出る（判断29）</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>画面でボタンを隠すだけでなくサーバ側でも拒否すること。表示ボタンの動きは画面で違う（従業員詳細＝読み取り専用モーダル／設定変更履歴一覧＝その従業員の従業員詳細へ遷移）</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>従業員詳細（設定変更履歴）／設定変更履歴一覧</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>T-D12 R-02</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 適用済みの設定を直したいとき ／ よくあるご質問 ＞ どなたが操作できますか</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>T-D12.png</t>
+        </is>
+      </c>
+      <c r="O73" s="12" t="inlineStr"/>
+      <c r="P73" s="13" t="inlineStr"/>
+      <c r="Q73" s="12" t="inlineStr"/>
+      <c r="R73" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R72"/>
+  <autoFilter ref="A12:R73"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O72">
+  <conditionalFormatting sqref="O13:O73">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5223,7 +5295,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$73,$A5)</f>
+        <f>COUNTIF($A$13:$A$75,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A5,$O$13:$O$73,"OK")</f>
+        <f>COUNTIFS($A$13:$A$75,$A5,$O$13:$O$75,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A5,$O$13:$O$73,"NG")</f>
+        <f>COUNTIFS($A$13:$A$75,$A5,$O$13:$O$75,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$73,$A6)</f>
+        <f>COUNTIF($A$13:$A$75,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A6,$O$13:$O$73,"OK")</f>
+        <f>COUNTIFS($A$13:$A$75,$A6,$O$13:$O$75,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A6,$O$13:$O$73,"NG")</f>
+        <f>COUNTIFS($A$13:$A$75,$A6,$O$13:$O$75,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$73,$A7)</f>
+        <f>COUNTIF($A$13:$A$75,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A7,$O$13:$O$73,"OK")</f>
+        <f>COUNTIFS($A$13:$A$75,$A7,$O$13:$O$75,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A7,$O$13:$O$73,"NG")</f>
+        <f>COUNTIFS($A$13:$A$75,$A7,$O$13:$O$75,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$73,$A8)</f>
+        <f>COUNTIF($A$13:$A$75,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A8,$O$13:$O$73,"OK")</f>
+        <f>COUNTIFS($A$13:$A$75,$A8,$O$13:$O$75,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A8,$O$13:$O$73,"NG")</f>
+        <f>COUNTIFS($A$13:$A$75,$A8,$O$13:$O$75,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$73,$A9)</f>
+        <f>COUNTIF($A$13:$A$75,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A9,$O$13:$O$73,"OK")</f>
+        <f>COUNTIFS($A$13:$A$75,$A9,$O$13:$O$75,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A9,$O$13:$O$73,"NG")</f>
+        <f>COUNTIFS($A$13:$A$75,$A9,$O$13:$O$75,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$73,$A10)</f>
+        <f>COUNTIF($A$13:$A$75,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A10,$O$13:$O$73,"OK")</f>
+        <f>COUNTIFS($A$13:$A$75,$A10,$O$13:$O$75,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$73,$A10,$O$13:$O$73,"NG")</f>
+        <f>COUNTIFS($A$13:$A$75,$A10,$O$13:$O$75,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$73,"L0*",$O$13:$O$73,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$73,"L1*",$O$13:$O$73,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$73,"L0*",$O$13:$O$73,"OK")+COUNTIFS($E$13:$E$73,"L1*",$O$13:$O$73,"OK")&lt;COUNTIF($E$13:$E$73,"L0*")+COUNTIF($E$13:$E$73,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$75,"L0*",$O$13:$O$75,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$75,"L1*",$O$13:$O$75,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$75,"L0*",$O$13:$O$75,"OK")+COUNTIFS($E$13:$E$75,"L1*",$O$13:$O$75,"OK")&lt;COUNTIF($E$13:$E$75,"L0*")+COUNTIF($E$13:$E$75,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -5271,14 +5271,158 @@
       <c r="Q73" s="12" t="inlineStr"/>
       <c r="R73" s="12" t="inlineStr"/>
     </row>
+    <row r="74" ht="94" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>M2 金額が算式どおりに出る</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>計算：欠けても合計が欠けない</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>AC-62</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>取込エラーがある行でも金額の出し方が決まっている</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>交通費が設定されていない従業員は交通費0円で計算され、金額が表示される（空欄=0件）。出退勤の打刻漏れがある日は出勤日に数えず日次の行も作らない。エラーの絞り込み（交通費欠損・出退勤打刻漏れ）でその行だけを抽出できる（判断30）</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>条件付きGo可</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>打刻漏れは想定労働日数（直近3か月の平均出勤日数・判断28）に効く。訂正は勤怠システム側で直して取り込み直す。締め済みなら締めを解除してから取り込み直す</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>給与実績一覧（月別・日別）</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>T-A10</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M74" s="9" t="inlineStr"/>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t>T-A10.png</t>
+        </is>
+      </c>
+      <c r="O74" s="12" t="inlineStr"/>
+      <c r="P74" s="13" t="inlineStr"/>
+      <c r="Q74" s="12" t="inlineStr"/>
+      <c r="R74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75" ht="94" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>M4 顧客とCSが自分で運用できる</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>原則②：起きた記録は書き換えない</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>AC-63</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>退職者を外しても過去の実績が残る</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>在籍状態を「退職」にすると従業員一覧から外れる。給与実績一覧の過去月にはその従業員が出続け、金額が1円も変わらない。設定変更履歴も残る。実績が1件でもある従業員は削除できない（削除成功=0件）。実績が無い従業員は削除できる（判断31）</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>画面でボタンを隠すだけでなくサーバ側でも拒否すること。退職は削除ではないので、履歴も実績も物理削除しない</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>従業員一覧／従業員詳細／給与実績一覧</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>T-D13 R-03</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員を探す・削除する ／ よくあるご質問 ＞ 設定が保存できません</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t>T-D13.png</t>
+        </is>
+      </c>
+      <c r="O75" s="12" t="inlineStr"/>
+      <c r="P75" s="13" t="inlineStr"/>
+      <c r="Q75" s="12" t="inlineStr"/>
+      <c r="R75" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R73"/>
+  <autoFilter ref="A12:R75"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O73">
+  <conditionalFormatting sqref="O13:O75">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5295,7 +5439,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -1504,7 +1504,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>店舗5店の合計 − 全社 = 0円（1,461,312円）</t>
+          <t>店舗5店の合計 − 全社 = 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>全行で差分=0円（EMP-001=338,000／EMP-002=285,250／EMP-003=144,000／EMP-005=382,812／EMP-007=311,250）</t>
+          <t>全行で差分=0円（実績給与 EMP-001=357,600／EMP-002=300,250／EMP-003=154,300／EMP-005=407,912／EMP-007=341,250）</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>332,727円（320,000×8/22＋340,000×14/22）</t>
+          <t>350,727円（320,000×8/22＋340,000×14/22＝332,727 ＋ 月額交通費18,000。判断23）</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>144,000円（差分0）</t>
+          <t>153,000円（1,200×所定120h ＋ 日額交通費600×想定労働日数15。判断23。差分0）</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4335,7 +4335,7 @@
       <c r="Q60" s="12" t="inlineStr"/>
       <c r="R60" s="12" t="inlineStr"/>
     </row>
-    <row r="61" ht="94" customHeight="1">
+    <row r="61" ht="109" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される</t>
+          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される。給与実績一覧の設定編集モーダルにも適用日付の入力欄があり、未来日＝予約／当日・過去＝即時／締め済み期間は警告して反映しない（従業員詳細と同じ規則。食い違い=0件。判断32）</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>T-A09 R-06</t>
+          <t>T-D11 T-A09 R-06</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
@@ -4399,7 +4399,7 @@
       <c r="M61" s="9" t="inlineStr"/>
       <c r="N61" s="9" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>T-D11.png</t>
         </is>
       </c>
       <c r="O61" s="12" t="inlineStr"/>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4335,7 +4335,7 @@
       <c r="Q60" s="12" t="inlineStr"/>
       <c r="R60" s="12" t="inlineStr"/>
     </row>
-    <row r="61" ht="109" customHeight="1">
+    <row r="61" ht="154" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される。給与実績一覧の設定編集モーダルにも適用日付の入力欄があり、未来日＝予約／当日・過去＝即時／締め済み期間は警告して反映しない（従業員詳細と同じ規則。食い違い=0件。判断32）</t>
+          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される。設定を変えられるのは従業員詳細だけ。給与実績一覧は従業員設定の列を持たず、「従業員詳細」列から遷移する（給与実績一覧での設定編集=0件。判断33）。判断33）。食い違い=0件。判断32）</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>設定更新の処理を1箇所に集約し、両方の画面から同じ処理を呼ぶ。※この集約はM1（データ基盤）の時点で作る。後から画面ごとに分かれた実装を統合するのは困難。判定はモーダルが実装されるM4で行う</t>
+          <t>設定更新の処理を1箇所に集約し、両方の画面から同じ処理を呼ぶ。※この集約はM1（データ基盤）の時点で作る。後から画面ごとに分かれた実装を統合するのは困難。判定はモーダルが実装されるM4で行う。画面の入口は従業員詳細だけになったが、設定インポートも設定を書き込むため、取込経路との共通化はR-06で確認する</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -4368,7 +4368,7 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される。設定を変えられるのは従業員詳細だけ。給与実績一覧は従業員設定の列を持たず、「従業員詳細」列から遷移する（給与実績一覧での設定編集=0件。判断33）。判断33）。食い違い=0件。判断32）</t>
+          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される。設定を変えられるのは従業員詳細だけ。給与実績一覧の「従業員設定」は表示のみのモーダルで、保存ボタンが無く、中の「従業員詳細」ボタンから直しに行く（給与実績一覧での保存=0件。判断33）。判断33）。判断33）。食い違い=0件。判断32）</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R75"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$75,$A5)</f>
+        <f>COUNTIF($A$13:$A$79,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A5,$O$13:$O$75,"OK")</f>
+        <f>COUNTIFS($A$13:$A$79,$A5,$O$13:$O$79,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A5,$O$13:$O$75,"NG")</f>
+        <f>COUNTIFS($A$13:$A$79,$A5,$O$13:$O$79,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$75,$A6)</f>
+        <f>COUNTIF($A$13:$A$79,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A6,$O$13:$O$75,"OK")</f>
+        <f>COUNTIFS($A$13:$A$79,$A6,$O$13:$O$79,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A6,$O$13:$O$75,"NG")</f>
+        <f>COUNTIFS($A$13:$A$79,$A6,$O$13:$O$79,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$75,$A7)</f>
+        <f>COUNTIF($A$13:$A$79,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A7,$O$13:$O$75,"OK")</f>
+        <f>COUNTIFS($A$13:$A$79,$A7,$O$13:$O$79,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A7,$O$13:$O$75,"NG")</f>
+        <f>COUNTIFS($A$13:$A$79,$A7,$O$13:$O$79,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$75,$A8)</f>
+        <f>COUNTIF($A$13:$A$79,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A8,$O$13:$O$75,"OK")</f>
+        <f>COUNTIFS($A$13:$A$79,$A8,$O$13:$O$79,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A8,$O$13:$O$75,"NG")</f>
+        <f>COUNTIFS($A$13:$A$79,$A8,$O$13:$O$79,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$75,$A9)</f>
+        <f>COUNTIF($A$13:$A$79,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A9,$O$13:$O$75,"OK")</f>
+        <f>COUNTIFS($A$13:$A$79,$A9,$O$13:$O$79,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A9,$O$13:$O$75,"NG")</f>
+        <f>COUNTIFS($A$13:$A$79,$A9,$O$13:$O$79,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$75,$A10)</f>
+        <f>COUNTIF($A$13:$A$79,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A10,$O$13:$O$75,"OK")</f>
+        <f>COUNTIFS($A$13:$A$79,$A10,$O$13:$O$79,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$75,$A10,$O$13:$O$75,"NG")</f>
+        <f>COUNTIFS($A$13:$A$79,$A10,$O$13:$O$79,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$75,"L0*",$O$13:$O$75,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$75,"L1*",$O$13:$O$75,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$75,"L0*",$O$13:$O$75,"OK")+COUNTIFS($E$13:$E$75,"L1*",$O$13:$O$75,"OK")&lt;COUNTIF($E$13:$E$75,"L0*")+COUNTIF($E$13:$E$75,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$79,"L0*",$O$13:$O$79,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$79,"L1*",$O$13:$O$79,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$79,"L0*",$O$13:$O$79,"OK")+COUNTIFS($E$13:$E$79,"L1*",$O$13:$O$79,"OK")&lt;COUNTIF($E$13:$E$79,"L0*")+COUNTIF($E$13:$E$79,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -5415,14 +5415,302 @@
       <c r="Q75" s="12" t="inlineStr"/>
       <c r="R75" s="12" t="inlineStr"/>
     </row>
+    <row r="76" ht="94" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>M2 金額が算式どおりに出る</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>計算：過去月の想定労働日数は動かさない</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>AC-64</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>過去月の概算給与が後から変わらない</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>打刻がある月は その月の実出勤日数 が想定労働日数として使われる。新しい月を取り込んでも過去月の概算給与が1円も変わらない（差分=0円）。打刻が無い月だけ直近3か月の平均が使われる（判断34）</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>当月は途中まで打刻が入るが、月の途中では直近3か月の平均を使う（今日までの出勤日数を使うと月初の概算が極端に小さくなる）。月が締まった時点でその月の実出勤日数に確定する</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>給与実績一覧（月別・概算）</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>C-020</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="M76" s="9" t="inlineStr"/>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t>C-020.png</t>
+        </is>
+      </c>
+      <c r="O76" s="12" t="inlineStr"/>
+      <c r="P76" s="13" t="inlineStr"/>
+      <c r="Q76" s="12" t="inlineStr"/>
+      <c r="R76" s="12" t="inlineStr"/>
+    </row>
+    <row r="77" ht="49" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>M2 金額が算式どおりに出る</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>計算：概算は在籍者だけ</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>AC-65</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>退職者が概算に含まれない</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>在籍状態が「退職」の従業員は概算モードに出ない（出現=0件）。実績モードには出て、金額が1円も変わらない（判断35）</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>条件付きGo可</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>退職日は持たない。在籍状態だけで判定する</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>給与実績一覧（月別・日別／概算）</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>T-D14</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr"/>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>T-D14.png</t>
+        </is>
+      </c>
+      <c r="O77" s="12" t="inlineStr"/>
+      <c r="P77" s="13" t="inlineStr"/>
+      <c r="Q77" s="12" t="inlineStr"/>
+      <c r="R77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78" ht="79" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>M1 過去が動かない構造ができる</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>設定が適用日付つきで保存され、履歴が積まれる。同じ従業員コードが二重に登録されない</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>原則①：上書きではなく積み重ね</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>AC-66</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>同じ適用日付が複数あってもどちらが有効か決まる</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>同じ適用日付で2件保存すると、編集日時が新しいほうが有効になり、古いほうも履歴に残る（消失=0件）。将来日付の予約を2件入れると両方残り、適用日付の順に効く。有効な行にだけステータスが付く（判断36）</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>上書きで消さないこと。消すとAC-07・AC-08（原因を追える）が破れる</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>従業員詳細（設定変更履歴）／設定変更履歴一覧</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>T-D14 R-01</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する ／ ケース別 ＞ 数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="M78" s="9" t="inlineStr"/>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t>T-D14.png</t>
+        </is>
+      </c>
+      <c r="O78" s="12" t="inlineStr"/>
+      <c r="P78" s="13" t="inlineStr"/>
+      <c r="Q78" s="12" t="inlineStr"/>
+      <c r="R78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79" ht="64" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>M2 金額が算式どおりに出る</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>計算：交通費は按分しない</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>AC-67</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>L2 次段階</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>月の途中で交通費を改定しても実費と合う</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>月額交通費を月の途中で改定した月は旧額のまま、翌月から新額になる（日割り=0件）。日額交通費は適用日付以降の出勤日から新額になる（判断37）</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>条件付きGo可</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>定期代は月単位で購入するため、月額は日割りしない。日額は日ごとの実費なので日単位で切り替える</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
+          <t>給与実績一覧（月別・日別）</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>C-021</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="M79" s="9" t="inlineStr"/>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t>C-021.png</t>
+        </is>
+      </c>
+      <c r="O79" s="12" t="inlineStr"/>
+      <c r="P79" s="13" t="inlineStr"/>
+      <c r="Q79" s="12" t="inlineStr"/>
+      <c r="R79" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R75"/>
+  <autoFilter ref="A12:R79"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O75">
+  <conditionalFormatting sqref="O13:O79">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5439,7 +5727,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受入条件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$12:$R$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R79"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,15 +614,15 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="6">
-        <f>COUNTIF($A$13:$A$79,$A5)</f>
+        <f>COUNTIF($A$13:$A$80,$A5)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A5,$O$13:$O$79,"OK")</f>
+        <f>COUNTIFS($A$13:$A$80,$A5,$O$13:$O$80,"OK")</f>
         <v/>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A5,$O$13:$O$79,"NG")</f>
+        <f>COUNTIFS($A$13:$A$80,$A5,$O$13:$O$80,"NG")</f>
         <v/>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -646,15 +646,15 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6">
-        <f>COUNTIF($A$13:$A$79,$A6)</f>
+        <f>COUNTIF($A$13:$A$80,$A6)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A6,$O$13:$O$79,"OK")</f>
+        <f>COUNTIFS($A$13:$A$80,$A6,$O$13:$O$80,"OK")</f>
         <v/>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A6,$O$13:$O$79,"NG")</f>
+        <f>COUNTIFS($A$13:$A$80,$A6,$O$13:$O$80,"NG")</f>
         <v/>
       </c>
       <c r="H6" s="6" t="n"/>
@@ -678,15 +678,15 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6">
-        <f>COUNTIF($A$13:$A$79,$A7)</f>
+        <f>COUNTIF($A$13:$A$80,$A7)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A7,$O$13:$O$79,"OK")</f>
+        <f>COUNTIFS($A$13:$A$80,$A7,$O$13:$O$80,"OK")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A7,$O$13:$O$79,"NG")</f>
+        <f>COUNTIFS($A$13:$A$80,$A7,$O$13:$O$80,"NG")</f>
         <v/>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -710,15 +710,15 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6">
-        <f>COUNTIF($A$13:$A$79,$A8)</f>
+        <f>COUNTIF($A$13:$A$80,$A8)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A8,$O$13:$O$79,"OK")</f>
+        <f>COUNTIFS($A$13:$A$80,$A8,$O$13:$O$80,"OK")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A8,$O$13:$O$79,"NG")</f>
+        <f>COUNTIFS($A$13:$A$80,$A8,$O$13:$O$80,"NG")</f>
         <v/>
       </c>
       <c r="H8" s="6" t="n"/>
@@ -742,15 +742,15 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6">
-        <f>COUNTIF($A$13:$A$79,$A9)</f>
+        <f>COUNTIF($A$13:$A$80,$A9)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A9,$O$13:$O$79,"OK")</f>
+        <f>COUNTIFS($A$13:$A$80,$A9,$O$13:$O$80,"OK")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A9,$O$13:$O$79,"NG")</f>
+        <f>COUNTIFS($A$13:$A$80,$A9,$O$13:$O$80,"NG")</f>
         <v/>
       </c>
       <c r="H9" s="6" t="n"/>
@@ -774,15 +774,15 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6">
-        <f>COUNTIF($A$13:$A$79,$A10)</f>
+        <f>COUNTIF($A$13:$A$80,$A10)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A10,$O$13:$O$79,"OK")</f>
+        <f>COUNTIFS($A$13:$A$80,$A10,$O$13:$O$80,"OK")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>COUNTIFS($A$13:$A$79,$A10,$O$13:$O$79,"NG")</f>
+        <f>COUNTIFS($A$13:$A$80,$A10,$O$13:$O$80,"NG")</f>
         <v/>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS($E$13:$E$79,"L0*",$O$13:$O$79,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$79,"L1*",$O$13:$O$79,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$79,"L0*",$O$13:$O$79,"OK")+COUNTIFS($E$13:$E$79,"L1*",$O$13:$O$79,"OK")&lt;COUNTIF($E$13:$E$79,"L0*")+COUNTIF($E$13:$E$79,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
+        <f>IF(COUNTIFS($E$13:$E$80,"L0*",$O$13:$O$80,"NG")&gt;0,"✗ リリース不可（L0にNG）",IF(COUNTIFS($E$13:$E$80,"L1*",$O$13:$O$80,"NG")&gt;0,"△ 設計MVP未達（L1にNG）",IF(COUNTIFS($E$13:$E$80,"L0*",$O$13:$O$80,"OK")+COUNTIFS($E$13:$E$80,"L1*",$O$13:$O$80,"OK")&lt;COUNTIF($E$13:$E$80,"L0*")+COUNTIF($E$13:$E$80,"L1*"),"進行中（L0・L1に未判定あり）","◎ リリース可（L0・L1すべてOK）")))</f>
         <v/>
       </c>
     </row>
@@ -5703,14 +5703,86 @@
       <c r="Q79" s="12" t="inlineStr"/>
       <c r="R79" s="12" t="inlineStr"/>
     </row>
+    <row r="80" ht="139" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>M4 顧客とCSが自分で運用できる</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>入出力：登録の手間を減らすが、設定は必ず埋めさせる</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>AC-68</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>L2 次段階</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>外部勤怠の新しい従業員を自動で追加でき、設定漏れが見える</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>連携設定に「新しい従業員を自動で追加する」のチェックボックスがあり、既定はOFF。OFFなら対応表に無い外部IDは取り込まれず件数と理由が出る（黙って登録=0件）。ONなら従業員が自動追加され、従業員ID・従業員コード・在籍状態=在籍・適用日付=取込対象月の初日 が入り、給与設定は空、外部ID対応表に行が1件増える。自動追加された従業員はエラーの絞り込み「給与設定が未入力」で抽出できる（判断38）</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>条件付きGo可</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>チェックボックスの置き場所は連携設定（ラクミー経営管理の既存画面。D7）。従業員管理の中では完結しない。自動追加は入力の手間を減らすものであって、設定を入れなくてよくなるわけではない</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>連携設定／実績の取込結果／従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>T-I21</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M80" s="9" t="inlineStr"/>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>T-I21.png</t>
+        </is>
+      </c>
+      <c r="O80" s="12" t="inlineStr"/>
+      <c r="P80" s="13" t="inlineStr"/>
+      <c r="Q80" s="12" t="inlineStr"/>
+      <c r="R80" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:R79"/>
+  <autoFilter ref="A12:R80"/>
   <mergeCells count="3">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="B11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="O13:O79">
+  <conditionalFormatting sqref="O13:O80">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -5727,7 +5799,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="O13:O79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O13:O80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5703,7 +5703,7 @@
       <c r="Q79" s="12" t="inlineStr"/>
       <c r="R79" s="12" t="inlineStr"/>
     </row>
-    <row r="80" ht="139" customHeight="1">
+    <row r="80" ht="169" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>連携設定に「新しい従業員を自動で追加する」のチェックボックスがあり、既定はOFF。OFFなら対応表に無い外部IDは取り込まれず件数と理由が出る（黙って登録=0件）。ONなら従業員が自動追加され、従業員ID・従業員コード・在籍状態=在籍・適用日付=取込対象月の初日 が入り、給与設定は空、外部ID対応表に行が1件増える。自動追加された従業員はエラーの絞り込み「給与設定が未入力」で抽出できる（判断38）</t>
+          <t>連携設定に「新しい従業員を自動で追加する」のチェックボックスがあり、既定はOFF。OFFなら対応表に無い外部IDは取り込まれず件数と理由が出る（黙って登録=0件）。ONなら従業員が自動追加され、従業員ID・従業員コード・在籍状態=在籍・適用日付=取込対象月の初日 が入り、給与設定は空、外部ID対応表に行が1件増える。自動追加された従業員は、従業員一覧の絞り込み「設定＝給与設定が未入力」と、給与実績一覧の絞り込み「エラー＝給与設定が未入力」の両方で抽出できる（判断38）</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">

--- a/20260805_従業員管理_01_確認表.xlsx
+++ b/20260805_従業員管理_01_確認表.xlsx
@@ -5415,7 +5415,7 @@
       <c r="Q75" s="12" t="inlineStr"/>
       <c r="R75" s="12" t="inlineStr"/>
     </row>
-    <row r="76" ht="94" customHeight="1">
+    <row r="76" ht="124" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>打刻がある月は その月の実出勤日数 が想定労働日数として使われる。新しい月を取り込んでも過去月の概算給与が1円も変わらない（差分=0円）。打刻が無い月だけ直近3か月の平均が使われる（判断34）</t>
+          <t>想定労働日数は、その月を最初に計算したときの値をスナップショットとして保存し、以後動かさない。新しい月を取り込んでも過去月の概算給与が1円も変わらない（差分=0円）。入力値があればその値、無ければ直近3か月の平均出勤日数を求めて保存する（判断43）</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>当月は途中まで打刻が入るが、月の途中では直近3か月の平均を使う（今日までの出勤日数を使うと月初の概算が極端に小さくなる）。月が締まった時点でその月の実出勤日数に確定する</t>
+          <t>data/05（月次の実績レコード）に想定労働日数の列があり、その月に使った分母を保存している。締めのスナップショット（AC-16）より前、その月を最初に計算した時点で固定する。想定労働日数と勤務日数は別の値なので、同じ値になってはいけない</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
